--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ КИ/дв 02,07,26 млрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ КИ/дв 02,07,26 млрсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\02,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDDC578-9005-43EA-BD09-014D233FF9AB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E575A28-DCD0-4C3D-838C-47CF4EBA7E13}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="253">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -1239,7 +1239,9 @@
     <col min="21" max="27" width="6" customWidth="1"/>
     <col min="28" max="28" width="42" customWidth="1"/>
     <col min="29" max="29" width="7" customWidth="1"/>
-    <col min="30" max="49" width="3" customWidth="1"/>
+    <col min="30" max="30" width="8" customWidth="1"/>
+    <col min="31" max="32" width="6.85546875" customWidth="1"/>
+    <col min="33" max="49" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
@@ -1504,10 +1506,16 @@
         <v>30</v>
       </c>
       <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
+      <c r="AC4" s="1" t="s">
+        <v>252</v>
+      </c>
       <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
+      <c r="AE4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="AG4" s="1"/>
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
@@ -1610,9 +1618,18 @@
         <f>SUM(AC6:AC499)</f>
         <v>9944</v>
       </c>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
+      <c r="AD5" s="4">
+        <f>SUM(AD6:AD499)</f>
+        <v>3783.9767999999995</v>
+      </c>
+      <c r="AE5" s="4">
+        <f t="shared" ref="AE5:AF5" si="2">SUM(AE6:AE499)</f>
+        <v>12982.384504719999</v>
+      </c>
+      <c r="AF5" s="4">
+        <f t="shared" si="2"/>
+        <v>17331.683679999995</v>
+      </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
@@ -1662,7 +1679,7 @@
         <v>280.5</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" ref="L6:L37" si="2">E6-K6</f>
+        <f t="shared" ref="L6:L37" si="3">E6-K6</f>
         <v>-11.444000000000017</v>
       </c>
       <c r="M6" s="1"/>
@@ -1710,9 +1727,18 @@
         <f>ROUND(G6*R6,0)</f>
         <v>0</v>
       </c>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="1"/>
+      <c r="AD6" s="1">
+        <f>Q6*G6</f>
+        <v>53.811199999999999</v>
+      </c>
+      <c r="AE6" s="1">
+        <f>O6*G6</f>
+        <v>600</v>
+      </c>
+      <c r="AF6" s="1">
+        <f>P6*G6</f>
+        <v>0</v>
+      </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
@@ -1762,7 +1788,7 @@
         <v>921.45</v>
       </c>
       <c r="L7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>14.913000000000011</v>
       </c>
       <c r="M7" s="1"/>
@@ -1774,7 +1800,7 @@
         <v>875.09742000000006</v>
       </c>
       <c r="Q7" s="1">
-        <f t="shared" ref="Q7:Q70" si="3">E7/5</f>
+        <f t="shared" ref="Q7:Q70" si="4">E7/5</f>
         <v>187.27260000000001</v>
       </c>
       <c r="R7" s="5">
@@ -1782,11 +1808,11 @@
         <v>640.29417999999987</v>
       </c>
       <c r="S7" s="1">
-        <f t="shared" ref="S7:S70" si="4">(F7+O7+P7+R7)/Q7</f>
+        <f t="shared" ref="S7:S70" si="5">(F7+O7+P7+R7)/Q7</f>
         <v>10.999999999999998</v>
       </c>
       <c r="T7" s="1">
-        <f t="shared" ref="T7:T70" si="5">(F7+O7+P7)/Q7</f>
+        <f t="shared" ref="T7:T70" si="6">(F7+O7+P7)/Q7</f>
         <v>7.5809510841415131</v>
       </c>
       <c r="U7" s="1">
@@ -1812,12 +1838,21 @@
       </c>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1">
-        <f t="shared" ref="AC7:AC70" si="6">ROUND(G7*R7,0)</f>
+        <f t="shared" ref="AC7:AC70" si="7">ROUND(G7*R7,0)</f>
         <v>640</v>
       </c>
-      <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="1"/>
+      <c r="AD7" s="1">
+        <f t="shared" ref="AD7:AD70" si="8">Q7*G7</f>
+        <v>187.27260000000001</v>
+      </c>
+      <c r="AE7" s="1">
+        <f t="shared" ref="AE7:AE70" si="9">O7*G7</f>
+        <v>0</v>
+      </c>
+      <c r="AF7" s="1">
+        <f t="shared" ref="AF7:AF70" si="10">P7*G7</f>
+        <v>875.09742000000006</v>
+      </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
@@ -1867,7 +1902,7 @@
         <v>922.9</v>
       </c>
       <c r="L8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-3.8179999999999836</v>
       </c>
       <c r="M8" s="1"/>
@@ -1879,7 +1914,7 @@
         <v>841.85323999999991</v>
       </c>
       <c r="Q8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>183.81639999999999</v>
       </c>
       <c r="R8" s="5">
@@ -1887,11 +1922,11 @@
         <v>633.55316000000005</v>
       </c>
       <c r="S8" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="T8" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.553337134227414</v>
       </c>
       <c r="U8" s="1">
@@ -1917,12 +1952,21 @@
       </c>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>634</v>
       </c>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1"/>
+      <c r="AD8" s="1">
+        <f t="shared" si="8"/>
+        <v>183.81639999999999</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" si="10"/>
+        <v>841.85323999999991</v>
+      </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
@@ -1970,7 +2014,7 @@
         <v>20</v>
       </c>
       <c r="L9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-13</v>
       </c>
       <c r="M9" s="1"/>
@@ -1980,18 +2024,18 @@
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.4</v>
       </c>
       <c r="R9" s="5"/>
       <c r="S9" s="1">
-        <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="T9" s="1">
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
+      <c r="T9" s="1">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
       <c r="U9" s="1">
         <v>2</v>
       </c>
@@ -2017,12 +2061,21 @@
         <v>244</v>
       </c>
       <c r="AC9" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1"/>
+      <c r="AD9" s="1">
+        <f t="shared" si="8"/>
+        <v>0.55999999999999994</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF9" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
@@ -2072,7 +2125,7 @@
         <v>339</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-6</v>
       </c>
       <c r="M10" s="1"/>
@@ -2084,19 +2137,19 @@
         <v>167.8</v>
       </c>
       <c r="Q10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>66.599999999999994</v>
       </c>
       <c r="R10" s="5">
-        <f t="shared" ref="R10:R14" si="7">12*Q10-P10-O10-F10</f>
+        <f t="shared" ref="R10:R14" si="11">12*Q10-P10-O10-F10</f>
         <v>70.399999999999864</v>
       </c>
       <c r="S10" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.999999999999998</v>
       </c>
       <c r="T10" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10.942942942942944</v>
       </c>
       <c r="U10" s="1">
@@ -2122,12 +2175,21 @@
       </c>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
+      <c r="AD10" s="1">
+        <f t="shared" si="8"/>
+        <v>29.97</v>
+      </c>
+      <c r="AE10" s="1">
+        <f t="shared" si="9"/>
+        <v>119.7</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" si="10"/>
+        <v>75.510000000000005</v>
+      </c>
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
@@ -2177,7 +2239,7 @@
         <v>404</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-14</v>
       </c>
       <c r="M11" s="1"/>
@@ -2187,19 +2249,19 @@
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>78</v>
       </c>
       <c r="R11" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>19</v>
       </c>
       <c r="S11" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T11" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.756410256410257</v>
       </c>
       <c r="U11" s="1">
@@ -2225,12 +2287,21 @@
       </c>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1"/>
+      <c r="AD11" s="1">
+        <f t="shared" si="8"/>
+        <v>35.1</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
@@ -2280,7 +2351,7 @@
         <v>101</v>
       </c>
       <c r="L12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-11</v>
       </c>
       <c r="M12" s="1"/>
@@ -2292,19 +2363,19 @@
         <v>39.080000000000013</v>
       </c>
       <c r="Q12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="R12" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>78.919999999999987</v>
       </c>
       <c r="S12" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T12" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.6155555555555559</v>
       </c>
       <c r="U12" s="1">
@@ -2330,12 +2401,21 @@
       </c>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
+      <c r="AD12" s="1">
+        <f t="shared" si="8"/>
+        <v>5.3999999999999995</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" si="10"/>
+        <v>11.724000000000004</v>
+      </c>
       <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
@@ -2385,7 +2465,7 @@
         <v>165</v>
       </c>
       <c r="L13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-12</v>
       </c>
       <c r="M13" s="1"/>
@@ -2395,18 +2475,18 @@
       </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>30.6</v>
       </c>
       <c r="R13" s="5"/>
       <c r="S13" s="1">
-        <f t="shared" si="4"/>
-        <v>14.15032679738562</v>
-      </c>
-      <c r="T13" s="1">
         <f t="shared" si="5"/>
         <v>14.15032679738562</v>
       </c>
+      <c r="T13" s="1">
+        <f t="shared" si="6"/>
+        <v>14.15032679738562</v>
+      </c>
       <c r="U13" s="1">
         <v>32.799999999999997</v>
       </c>
@@ -2430,12 +2510,21 @@
       </c>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="1"/>
+      <c r="AD13" s="1">
+        <f t="shared" si="8"/>
+        <v>5.2020000000000008</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" si="9"/>
+        <v>51.000000000000007</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
@@ -2485,7 +2574,7 @@
         <v>309.14</v>
       </c>
       <c r="L14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-48.25</v>
       </c>
       <c r="M14" s="1"/>
@@ -2495,19 +2584,19 @@
       </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>52.177999999999997</v>
       </c>
       <c r="R14" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>301.05499999999995</v>
       </c>
       <c r="S14" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T14" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.2302311318946693</v>
       </c>
       <c r="U14" s="1">
@@ -2533,12 +2622,21 @@
       </c>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>301</v>
       </c>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
+      <c r="AD14" s="1">
+        <f t="shared" si="8"/>
+        <v>52.177999999999997</v>
+      </c>
+      <c r="AE14" s="1">
+        <f t="shared" si="9"/>
+        <v>200</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
@@ -2588,7 +2686,7 @@
         <v>1659.5</v>
       </c>
       <c r="L15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-322.90699999999993</v>
       </c>
       <c r="M15" s="1"/>
@@ -2598,7 +2696,7 @@
       </c>
       <c r="P15" s="1"/>
       <c r="Q15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>267.3186</v>
       </c>
       <c r="R15" s="5">
@@ -2606,11 +2704,11 @@
         <v>1950.5427999999997</v>
       </c>
       <c r="S15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="T15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.7033030997468943</v>
       </c>
       <c r="U15" s="1">
@@ -2636,12 +2734,21 @@
       </c>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1951</v>
       </c>
-      <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-      <c r="AF15" s="1"/>
+      <c r="AD15" s="1">
+        <f t="shared" si="8"/>
+        <v>267.3186</v>
+      </c>
+      <c r="AE15" s="1">
+        <f t="shared" si="9"/>
+        <v>800</v>
+      </c>
+      <c r="AF15" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
@@ -2691,7 +2798,7 @@
         <v>78.7</v>
       </c>
       <c r="L16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.0120000000000005</v>
       </c>
       <c r="M16" s="1"/>
@@ -2703,18 +2810,18 @@
         <v>86.049840000000017</v>
       </c>
       <c r="Q16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.942399999999999</v>
       </c>
       <c r="R16" s="5"/>
       <c r="S16" s="1">
-        <f t="shared" si="4"/>
-        <v>13.37815622343942</v>
-      </c>
-      <c r="T16" s="1">
         <f t="shared" si="5"/>
         <v>13.37815622343942</v>
       </c>
+      <c r="T16" s="1">
+        <f t="shared" si="6"/>
+        <v>13.37815622343942</v>
+      </c>
       <c r="U16" s="1">
         <v>19.0762</v>
       </c>
@@ -2738,12 +2845,21 @@
       </c>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
+      <c r="AD16" s="1">
+        <f t="shared" si="8"/>
+        <v>16.942399999999999</v>
+      </c>
+      <c r="AE16" s="1">
+        <f t="shared" si="9"/>
+        <v>84.398234000000002</v>
+      </c>
+      <c r="AF16" s="1">
+        <f t="shared" si="10"/>
+        <v>86.049840000000017</v>
+      </c>
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
@@ -2793,7 +2909,7 @@
         <v>392.5</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-395.33199999999999</v>
       </c>
       <c r="M17" s="9"/>
@@ -2801,18 +2917,18 @@
       <c r="O17" s="9"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.56640000000000001</v>
       </c>
       <c r="R17" s="11"/>
       <c r="S17" s="9">
-        <f t="shared" si="4"/>
-        <v>0.5067090395480226</v>
-      </c>
-      <c r="T17" s="9">
         <f t="shared" si="5"/>
         <v>0.5067090395480226</v>
       </c>
+      <c r="T17" s="9">
+        <f t="shared" si="6"/>
+        <v>0.5067090395480226</v>
+      </c>
       <c r="U17" s="9">
         <v>-0.56640000000000001</v>
       </c>
@@ -2838,12 +2954,21 @@
         <v>57</v>
       </c>
       <c r="AC17" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-      <c r="AF17" s="1"/>
+      <c r="AD17" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG17" s="1"/>
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
@@ -2893,7 +3018,7 @@
         <v>56.6</v>
       </c>
       <c r="L18" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.8059999999999974</v>
       </c>
       <c r="M18" s="1"/>
@@ -2905,19 +3030,19 @@
         <v>111.65483999999999</v>
       </c>
       <c r="Q18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12.081199999999999</v>
       </c>
       <c r="R18" s="5">
-        <f t="shared" ref="R18:R50" si="8">12*Q18-P18-O18-F18</f>
+        <f t="shared" ref="R18:R50" si="12">12*Q18-P18-O18-F18</f>
         <v>14.67456000000001</v>
       </c>
       <c r="S18" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12.000000000000002</v>
       </c>
       <c r="T18" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10.785339204714763</v>
       </c>
       <c r="U18" s="1">
@@ -2943,12 +3068,21 @@
       </c>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
-      <c r="AF18" s="1"/>
+      <c r="AD18" s="1">
+        <f t="shared" si="8"/>
+        <v>12.081199999999999</v>
+      </c>
+      <c r="AE18" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="1">
+        <f t="shared" si="10"/>
+        <v>111.65483999999999</v>
+      </c>
       <c r="AG18" s="1"/>
       <c r="AH18" s="1"/>
       <c r="AI18" s="1"/>
@@ -2998,7 +3132,7 @@
         <v>36.409999999999997</v>
       </c>
       <c r="L19" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-4.3469999999999942</v>
       </c>
       <c r="M19" s="1"/>
@@ -3010,19 +3144,19 @@
         <v>24.039400000000011</v>
       </c>
       <c r="Q19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.4126000000000003</v>
       </c>
       <c r="R19" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>37.887799999999984</v>
       </c>
       <c r="S19" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T19" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.0916632879019437</v>
       </c>
       <c r="U19" s="1">
@@ -3048,12 +3182,21 @@
       </c>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>38</v>
       </c>
-      <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
-      <c r="AF19" s="1"/>
+      <c r="AD19" s="1">
+        <f t="shared" si="8"/>
+        <v>6.4126000000000003</v>
+      </c>
+      <c r="AE19" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="1">
+        <f t="shared" si="10"/>
+        <v>24.039400000000011</v>
+      </c>
       <c r="AG19" s="1"/>
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
@@ -3103,7 +3246,7 @@
         <v>534.26800000000003</v>
       </c>
       <c r="L20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27.038000000000011</v>
       </c>
       <c r="M20" s="1"/>
@@ -3113,19 +3256,19 @@
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>112.2612</v>
       </c>
       <c r="R20" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>313.79939999999988</v>
       </c>
       <c r="S20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.999999999999998</v>
       </c>
       <c r="T20" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.2047385917841602</v>
       </c>
       <c r="U20" s="1">
@@ -3151,12 +3294,21 @@
       </c>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>314</v>
       </c>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
-      <c r="AF20" s="1"/>
+      <c r="AD20" s="1">
+        <f t="shared" si="8"/>
+        <v>112.2612</v>
+      </c>
+      <c r="AE20" s="1">
+        <f t="shared" si="9"/>
+        <v>500</v>
+      </c>
+      <c r="AF20" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG20" s="1"/>
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
@@ -3206,7 +3358,7 @@
         <v>102.3</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-75.02</v>
       </c>
       <c r="M21" s="1"/>
@@ -3216,18 +3368,18 @@
       </c>
       <c r="P21" s="1"/>
       <c r="Q21" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.4560000000000004</v>
       </c>
       <c r="R21" s="5"/>
       <c r="S21" s="1">
-        <f t="shared" si="4"/>
-        <v>38.557872434017597</v>
-      </c>
-      <c r="T21" s="1">
         <f t="shared" si="5"/>
         <v>38.557872434017597</v>
       </c>
+      <c r="T21" s="1">
+        <f t="shared" si="6"/>
+        <v>38.557872434017597</v>
+      </c>
       <c r="U21" s="1">
         <v>17.258400000000002</v>
       </c>
@@ -3251,12 +3403,21 @@
       </c>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
-      <c r="AF21" s="1"/>
+      <c r="AD21" s="1">
+        <f t="shared" si="8"/>
+        <v>5.4560000000000004</v>
+      </c>
+      <c r="AE21" s="1">
+        <f t="shared" si="9"/>
+        <v>169.445752</v>
+      </c>
+      <c r="AF21" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG21" s="1"/>
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
@@ -3306,7 +3467,7 @@
         <v>259.42</v>
       </c>
       <c r="L22" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.007000000000005</v>
       </c>
       <c r="M22" s="1"/>
@@ -3318,19 +3479,19 @@
         <v>159.5375600000001</v>
       </c>
       <c r="Q22" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>53.085400000000007</v>
       </c>
       <c r="R22" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>28.313240000000064</v>
       </c>
       <c r="S22" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12.000000000000002</v>
       </c>
       <c r="T22" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.466647326760278</v>
       </c>
       <c r="U22" s="1">
@@ -3356,12 +3517,21 @@
       </c>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="AD22" s="1"/>
-      <c r="AE22" s="1"/>
-      <c r="AF22" s="1"/>
+      <c r="AD22" s="1">
+        <f t="shared" si="8"/>
+        <v>53.085400000000007</v>
+      </c>
+      <c r="AE22" s="1">
+        <f t="shared" si="9"/>
+        <v>180</v>
+      </c>
+      <c r="AF22" s="1">
+        <f t="shared" si="10"/>
+        <v>159.5375600000001</v>
+      </c>
       <c r="AG22" s="1"/>
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
@@ -3411,7 +3581,7 @@
         <v>40.22</v>
       </c>
       <c r="L23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-5.4810000000000016</v>
       </c>
       <c r="M23" s="1"/>
@@ -3423,19 +3593,19 @@
         <v>37.319239999999994</v>
       </c>
       <c r="Q23" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.9477999999999991</v>
       </c>
       <c r="R23" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>24.144359999999988</v>
       </c>
       <c r="S23" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.999999999999998</v>
       </c>
       <c r="T23" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.5248913325081315</v>
       </c>
       <c r="U23" s="1">
@@ -3461,12 +3631,21 @@
       </c>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
-      <c r="AD23" s="1"/>
-      <c r="AE23" s="1"/>
-      <c r="AF23" s="1"/>
+      <c r="AD23" s="1">
+        <f t="shared" si="8"/>
+        <v>6.9477999999999991</v>
+      </c>
+      <c r="AE23" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="1">
+        <f t="shared" si="10"/>
+        <v>37.319239999999994</v>
+      </c>
       <c r="AG23" s="1"/>
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
@@ -3516,7 +3695,7 @@
         <v>329.32</v>
       </c>
       <c r="L24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20.180999999999983</v>
       </c>
       <c r="M24" s="1"/>
@@ -3528,19 +3707,19 @@
         <v>155.3171200000001</v>
       </c>
       <c r="Q24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>69.900199999999998</v>
       </c>
       <c r="R24" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>159.37627999999989</v>
       </c>
       <c r="S24" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T24" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.7199452934326391</v>
       </c>
       <c r="U24" s="1">
@@ -3566,12 +3745,21 @@
       </c>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>159</v>
       </c>
-      <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
-      <c r="AF24" s="1"/>
+      <c r="AD24" s="1">
+        <f t="shared" si="8"/>
+        <v>69.900199999999998</v>
+      </c>
+      <c r="AE24" s="1">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+      <c r="AF24" s="1">
+        <f t="shared" si="10"/>
+        <v>155.3171200000001</v>
+      </c>
       <c r="AG24" s="1"/>
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
@@ -3621,7 +3809,7 @@
         <v>27.4</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-6.4619999999999997</v>
       </c>
       <c r="M25" s="1"/>
@@ -3633,18 +3821,18 @@
         <v>28.694680000000002</v>
       </c>
       <c r="Q25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.1875999999999998</v>
       </c>
       <c r="R25" s="5"/>
       <c r="S25" s="1">
-        <f t="shared" si="4"/>
-        <v>13.314232495940397</v>
-      </c>
-      <c r="T25" s="1">
         <f t="shared" si="5"/>
         <v>13.314232495940397</v>
       </c>
+      <c r="T25" s="1">
+        <f t="shared" si="6"/>
+        <v>13.314232495940397</v>
+      </c>
       <c r="U25" s="1">
         <v>4.7523999999999997</v>
       </c>
@@ -3668,12 +3856,21 @@
       </c>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
-      <c r="AF25" s="1"/>
+      <c r="AD25" s="1">
+        <f t="shared" si="8"/>
+        <v>4.1875999999999998</v>
+      </c>
+      <c r="AE25" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="1">
+        <f t="shared" si="10"/>
+        <v>28.694680000000002</v>
+      </c>
       <c r="AG25" s="1"/>
       <c r="AH25" s="1"/>
       <c r="AI25" s="1"/>
@@ -3723,7 +3920,7 @@
         <v>128.80000000000001</v>
       </c>
       <c r="L26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-8.9680000000000177</v>
       </c>
       <c r="M26" s="1"/>
@@ -3735,18 +3932,18 @@
         <v>334.14555999999999</v>
       </c>
       <c r="Q26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23.9664</v>
       </c>
       <c r="R26" s="5"/>
       <c r="S26" s="1">
-        <f t="shared" si="4"/>
-        <v>16.059998998598036</v>
-      </c>
-      <c r="T26" s="1">
         <f t="shared" si="5"/>
         <v>16.059998998598036</v>
       </c>
+      <c r="T26" s="1">
+        <f t="shared" si="6"/>
+        <v>16.059998998598036</v>
+      </c>
       <c r="U26" s="1">
         <v>38.5518</v>
       </c>
@@ -3770,12 +3967,21 @@
       </c>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD26" s="1"/>
-      <c r="AE26" s="1"/>
-      <c r="AF26" s="1"/>
+      <c r="AD26" s="1">
+        <f t="shared" si="8"/>
+        <v>23.9664</v>
+      </c>
+      <c r="AE26" s="1">
+        <f t="shared" si="9"/>
+        <v>81.295799999999986</v>
+      </c>
+      <c r="AF26" s="1">
+        <f t="shared" si="10"/>
+        <v>334.14555999999999</v>
+      </c>
       <c r="AG26" s="1"/>
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
@@ -3825,7 +4031,7 @@
         <v>371.11</v>
       </c>
       <c r="L27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-47.937000000000012</v>
       </c>
       <c r="M27" s="1"/>
@@ -3837,19 +4043,19 @@
         <v>366.00639999999981</v>
       </c>
       <c r="Q27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>64.634600000000006</v>
       </c>
       <c r="R27" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>114.12384000000003</v>
       </c>
       <c r="S27" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.999999999999998</v>
       </c>
       <c r="T27" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10.234322793055112</v>
       </c>
       <c r="U27" s="1">
@@ -3875,12 +4081,21 @@
       </c>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>114</v>
       </c>
-      <c r="AD27" s="1"/>
-      <c r="AE27" s="1"/>
-      <c r="AF27" s="1"/>
+      <c r="AD27" s="1">
+        <f t="shared" si="8"/>
+        <v>64.634600000000006</v>
+      </c>
+      <c r="AE27" s="1">
+        <f t="shared" si="9"/>
+        <v>272.92496000000023</v>
+      </c>
+      <c r="AF27" s="1">
+        <f t="shared" si="10"/>
+        <v>366.00639999999981</v>
+      </c>
       <c r="AG27" s="1"/>
       <c r="AH27" s="1"/>
       <c r="AI27" s="1"/>
@@ -3930,7 +4145,7 @@
         <v>502.4</v>
       </c>
       <c r="L28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-184.96799999999996</v>
       </c>
       <c r="M28" s="1"/>
@@ -3940,19 +4155,19 @@
       </c>
       <c r="P28" s="1"/>
       <c r="Q28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>63.486400000000003</v>
       </c>
       <c r="R28" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>487.62980000000005</v>
       </c>
       <c r="S28" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T28" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.3191455177801856</v>
       </c>
       <c r="U28" s="1">
@@ -3978,12 +4193,21 @@
       </c>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>488</v>
       </c>
-      <c r="AD28" s="1"/>
-      <c r="AE28" s="1"/>
-      <c r="AF28" s="1"/>
+      <c r="AD28" s="1">
+        <f t="shared" si="8"/>
+        <v>63.486400000000003</v>
+      </c>
+      <c r="AE28" s="1">
+        <f t="shared" si="9"/>
+        <v>300</v>
+      </c>
+      <c r="AF28" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
       <c r="AI28" s="1"/>
@@ -4033,7 +4257,7 @@
         <v>828.6</v>
       </c>
       <c r="L29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-454.31600000000003</v>
       </c>
       <c r="M29" s="1"/>
@@ -4045,18 +4269,18 @@
         <v>1298.42976</v>
       </c>
       <c r="Q29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>74.856799999999993</v>
       </c>
       <c r="R29" s="5"/>
       <c r="S29" s="1">
-        <f t="shared" si="4"/>
-        <v>30.730538307809045</v>
-      </c>
-      <c r="T29" s="1">
         <f t="shared" si="5"/>
         <v>30.730538307809045</v>
       </c>
+      <c r="T29" s="1">
+        <f t="shared" si="6"/>
+        <v>30.730538307809045</v>
+      </c>
       <c r="U29" s="1">
         <v>185.2568</v>
       </c>
@@ -4080,12 +4304,21 @@
       </c>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
-      <c r="AF29" s="1"/>
+      <c r="AD29" s="1">
+        <f t="shared" si="8"/>
+        <v>74.856799999999993</v>
+      </c>
+      <c r="AE29" s="1">
+        <f t="shared" si="9"/>
+        <v>1000</v>
+      </c>
+      <c r="AF29" s="1">
+        <f t="shared" si="10"/>
+        <v>1298.42976</v>
+      </c>
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
@@ -4131,7 +4364,7 @@
         <v>10.6</v>
       </c>
       <c r="L30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-10.6</v>
       </c>
       <c r="M30" s="1"/>
@@ -4143,20 +4376,20 @@
         <v>24.989159999999998</v>
       </c>
       <c r="Q30" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R30" s="5">
         <v>30</v>
       </c>
       <c r="S30" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T30" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="T30" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="U30" s="1">
         <v>0.64379999999999993</v>
       </c>
@@ -4180,12 +4413,21 @@
       </c>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
-      <c r="AF30" s="1"/>
+      <c r="AD30" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE30" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF30" s="1">
+        <f t="shared" si="10"/>
+        <v>24.989159999999998</v>
+      </c>
       <c r="AG30" s="1"/>
       <c r="AH30" s="1"/>
       <c r="AI30" s="1"/>
@@ -4235,7 +4477,7 @@
         <v>34.799999999999997</v>
       </c>
       <c r="L31" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.1489999999999938</v>
       </c>
       <c r="M31" s="1"/>
@@ -4245,19 +4487,19 @@
       </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.930200000000001</v>
       </c>
       <c r="R31" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>53.581087999999994</v>
       </c>
       <c r="S31" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12.000000000000002</v>
       </c>
       <c r="T31" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.268464402181757</v>
       </c>
       <c r="U31" s="1">
@@ -4283,12 +4525,21 @@
       </c>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>54</v>
       </c>
-      <c r="AD31" s="1"/>
-      <c r="AE31" s="1"/>
-      <c r="AF31" s="1"/>
+      <c r="AD31" s="1">
+        <f t="shared" si="8"/>
+        <v>6.930200000000001</v>
+      </c>
+      <c r="AE31" s="1">
+        <f t="shared" si="9"/>
+        <v>27.03931200000002</v>
+      </c>
+      <c r="AF31" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG31" s="1"/>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
@@ -4338,7 +4589,7 @@
         <v>100.5</v>
       </c>
       <c r="L32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13.677000000000007</v>
       </c>
       <c r="M32" s="1"/>
@@ -4350,19 +4601,19 @@
         <v>164.54040000000001</v>
       </c>
       <c r="Q32" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22.8354</v>
       </c>
       <c r="R32" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>93.548400000000015</v>
       </c>
       <c r="S32" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12.000000000000002</v>
       </c>
       <c r="T32" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.903360571743872</v>
       </c>
       <c r="U32" s="1">
@@ -4388,12 +4639,21 @@
       </c>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>94</v>
       </c>
-      <c r="AD32" s="1"/>
-      <c r="AE32" s="1"/>
-      <c r="AF32" s="1"/>
+      <c r="AD32" s="1">
+        <f t="shared" si="8"/>
+        <v>22.8354</v>
+      </c>
+      <c r="AE32" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF32" s="1">
+        <f t="shared" si="10"/>
+        <v>164.54040000000001</v>
+      </c>
       <c r="AG32" s="1"/>
       <c r="AH32" s="1"/>
       <c r="AI32" s="1"/>
@@ -4443,7 +4703,7 @@
         <v>72.7</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15.486999999999995</v>
       </c>
       <c r="M33" s="1"/>
@@ -4455,19 +4715,19 @@
         <v>146.64171999999999</v>
       </c>
       <c r="Q33" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.6374</v>
       </c>
       <c r="R33" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>62.580080000000002</v>
       </c>
       <c r="S33" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T33" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.451853447787089</v>
       </c>
       <c r="U33" s="1">
@@ -4493,12 +4753,21 @@
       </c>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
-      <c r="AD33" s="1"/>
-      <c r="AE33" s="1"/>
-      <c r="AF33" s="1"/>
+      <c r="AD33" s="1">
+        <f t="shared" si="8"/>
+        <v>17.6374</v>
+      </c>
+      <c r="AE33" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF33" s="1">
+        <f t="shared" si="10"/>
+        <v>146.64171999999999</v>
+      </c>
       <c r="AG33" s="1"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
@@ -4548,7 +4817,7 @@
         <v>56.4</v>
       </c>
       <c r="L34" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.0680000000000049</v>
       </c>
       <c r="M34" s="1"/>
@@ -4560,19 +4829,19 @@
         <v>104.70644</v>
       </c>
       <c r="Q34" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13.0936</v>
       </c>
       <c r="R34" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>43.947759999999995</v>
       </c>
       <c r="S34" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T34" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.643569377405754</v>
       </c>
       <c r="U34" s="1">
@@ -4598,12 +4867,21 @@
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>44</v>
       </c>
-      <c r="AD34" s="1"/>
-      <c r="AE34" s="1"/>
-      <c r="AF34" s="1"/>
+      <c r="AD34" s="1">
+        <f t="shared" si="8"/>
+        <v>13.0936</v>
+      </c>
+      <c r="AE34" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF34" s="1">
+        <f t="shared" si="10"/>
+        <v>104.70644</v>
+      </c>
       <c r="AG34" s="1"/>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
@@ -4653,7 +4931,7 @@
         <v>1333</v>
       </c>
       <c r="L35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-45</v>
       </c>
       <c r="M35" s="1"/>
@@ -4665,19 +4943,19 @@
         <v>1508.08</v>
       </c>
       <c r="Q35" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>257.60000000000002</v>
       </c>
       <c r="R35" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>687.12000000000035</v>
       </c>
       <c r="S35" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T35" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.3326086956521728</v>
       </c>
       <c r="U35" s="1">
@@ -4703,12 +4981,21 @@
       </c>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>275</v>
       </c>
-      <c r="AD35" s="1"/>
-      <c r="AE35" s="1"/>
-      <c r="AF35" s="1"/>
+      <c r="AD35" s="1">
+        <f t="shared" si="8"/>
+        <v>103.04000000000002</v>
+      </c>
+      <c r="AE35" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF35" s="1">
+        <f t="shared" si="10"/>
+        <v>603.23199999999997</v>
+      </c>
       <c r="AG35" s="1"/>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
@@ -4758,7 +5045,7 @@
         <v>290</v>
       </c>
       <c r="L36" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="M36" s="1"/>
@@ -4770,19 +5057,19 @@
         <v>335.95999999999992</v>
       </c>
       <c r="Q36" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>58.6</v>
       </c>
       <c r="R36" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>15.240000000000123</v>
       </c>
       <c r="S36" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T36" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.739931740614333</v>
       </c>
       <c r="U36" s="1">
@@ -4808,12 +5095,21 @@
       </c>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="AD36" s="1"/>
-      <c r="AE36" s="1"/>
-      <c r="AF36" s="1"/>
+      <c r="AD36" s="1">
+        <f t="shared" si="8"/>
+        <v>26.37</v>
+      </c>
+      <c r="AE36" s="1">
+        <f t="shared" si="9"/>
+        <v>90</v>
+      </c>
+      <c r="AF36" s="1">
+        <f t="shared" si="10"/>
+        <v>151.18199999999996</v>
+      </c>
       <c r="AG36" s="1"/>
       <c r="AH36" s="1"/>
       <c r="AI36" s="1"/>
@@ -4863,7 +5159,7 @@
         <v>435</v>
       </c>
       <c r="L37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-86</v>
       </c>
       <c r="M37" s="1"/>
@@ -4875,19 +5171,19 @@
         <v>598.42000000000007</v>
       </c>
       <c r="Q37" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>69.8</v>
       </c>
       <c r="R37" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5.5799999999999272</v>
       </c>
       <c r="S37" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T37" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.920057306590259</v>
       </c>
       <c r="U37" s="1">
@@ -4913,12 +5209,21 @@
       </c>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AD37" s="1"/>
-      <c r="AE37" s="1"/>
-      <c r="AF37" s="1"/>
+      <c r="AD37" s="1">
+        <f t="shared" si="8"/>
+        <v>27.92</v>
+      </c>
+      <c r="AE37" s="1">
+        <f t="shared" si="9"/>
+        <v>96.239999999999966</v>
+      </c>
+      <c r="AF37" s="1">
+        <f t="shared" si="10"/>
+        <v>239.36800000000005</v>
+      </c>
       <c r="AG37" s="1"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
@@ -4968,7 +5273,7 @@
         <v>61</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="9">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
         <v>-12</v>
       </c>
       <c r="M38" s="1"/>
@@ -4980,18 +5285,18 @@
         <v>59.239999999999988</v>
       </c>
       <c r="Q38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="R38" s="5"/>
       <c r="S38" s="1">
-        <f t="shared" si="4"/>
-        <v>15.085714285714282</v>
-      </c>
-      <c r="T38" s="1">
         <f t="shared" si="5"/>
         <v>15.085714285714282</v>
       </c>
+      <c r="T38" s="1">
+        <f t="shared" si="6"/>
+        <v>15.085714285714282</v>
+      </c>
       <c r="U38" s="1">
         <v>11.2</v>
       </c>
@@ -5015,12 +5320,21 @@
       </c>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD38" s="1"/>
-      <c r="AE38" s="1"/>
-      <c r="AF38" s="1"/>
+      <c r="AD38" s="1">
+        <f t="shared" si="8"/>
+        <v>3.9200000000000004</v>
+      </c>
+      <c r="AE38" s="1">
+        <f t="shared" si="9"/>
+        <v>35.04</v>
+      </c>
+      <c r="AF38" s="1">
+        <f t="shared" si="10"/>
+        <v>23.695999999999998</v>
+      </c>
       <c r="AG38" s="1"/>
       <c r="AH38" s="1"/>
       <c r="AI38" s="1"/>
@@ -5070,7 +5384,7 @@
         <v>25.8</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-19.988</v>
       </c>
       <c r="M39" s="1"/>
@@ -5082,18 +5396,18 @@
         <v>29.466840000000001</v>
       </c>
       <c r="Q39" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.1624000000000001</v>
       </c>
       <c r="R39" s="5"/>
       <c r="S39" s="1">
-        <f t="shared" si="4"/>
-        <v>56.099999999999994</v>
-      </c>
-      <c r="T39" s="1">
         <f t="shared" si="5"/>
         <v>56.099999999999994</v>
       </c>
+      <c r="T39" s="1">
+        <f t="shared" si="6"/>
+        <v>56.099999999999994</v>
+      </c>
       <c r="U39" s="1">
         <v>4.9401999999999999</v>
       </c>
@@ -5117,12 +5431,21 @@
       </c>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD39" s="1"/>
-      <c r="AE39" s="1"/>
-      <c r="AF39" s="1"/>
+      <c r="AD39" s="1">
+        <f t="shared" si="8"/>
+        <v>1.1624000000000001</v>
+      </c>
+      <c r="AE39" s="1">
+        <f t="shared" si="9"/>
+        <v>27.470800000000001</v>
+      </c>
+      <c r="AF39" s="1">
+        <f t="shared" si="10"/>
+        <v>29.466840000000001</v>
+      </c>
       <c r="AG39" s="1"/>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
@@ -5172,7 +5495,7 @@
         <v>301</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>122</v>
       </c>
       <c r="M40" s="1"/>
@@ -5184,19 +5507,19 @@
         <v>639.16</v>
       </c>
       <c r="Q40" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>84.6</v>
       </c>
       <c r="R40" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>243.03999999999996</v>
       </c>
       <c r="S40" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T40" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.1271867612293143</v>
       </c>
       <c r="U40" s="1">
@@ -5222,12 +5545,21 @@
       </c>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
-      <c r="AD40" s="1"/>
-      <c r="AE40" s="1"/>
-      <c r="AF40" s="1"/>
+      <c r="AD40" s="1">
+        <f t="shared" si="8"/>
+        <v>8.4599999999999991</v>
+      </c>
+      <c r="AE40" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF40" s="1">
+        <f t="shared" si="10"/>
+        <v>63.915999999999997</v>
+      </c>
       <c r="AG40" s="1"/>
       <c r="AH40" s="1"/>
       <c r="AI40" s="1"/>
@@ -5277,7 +5609,7 @@
         <v>209</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-39</v>
       </c>
       <c r="M41" s="1"/>
@@ -5289,19 +5621,19 @@
         <v>148.68</v>
       </c>
       <c r="Q41" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>34</v>
       </c>
       <c r="R41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>128.32</v>
       </c>
       <c r="S41" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T41" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.2258823529411771</v>
       </c>
       <c r="U41" s="1">
@@ -5327,12 +5659,21 @@
       </c>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>45</v>
       </c>
-      <c r="AD41" s="1"/>
-      <c r="AE41" s="1"/>
-      <c r="AF41" s="1"/>
+      <c r="AD41" s="1">
+        <f t="shared" si="8"/>
+        <v>11.899999999999999</v>
+      </c>
+      <c r="AE41" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF41" s="1">
+        <f t="shared" si="10"/>
+        <v>52.037999999999997</v>
+      </c>
       <c r="AG41" s="1"/>
       <c r="AH41" s="1"/>
       <c r="AI41" s="1"/>
@@ -5382,7 +5723,7 @@
         <v>121.6</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-14.134</v>
       </c>
       <c r="M42" s="1"/>
@@ -5394,19 +5735,19 @@
         <v>175.09031999999999</v>
       </c>
       <c r="Q42" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21.493199999999998</v>
       </c>
       <c r="R42" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>31.507079999999974</v>
       </c>
       <c r="S42" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T42" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10.534090782200883</v>
       </c>
       <c r="U42" s="1">
@@ -5432,12 +5773,21 @@
       </c>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="AD42" s="1"/>
-      <c r="AE42" s="1"/>
-      <c r="AF42" s="1"/>
+      <c r="AD42" s="1">
+        <f t="shared" si="8"/>
+        <v>21.493199999999998</v>
+      </c>
+      <c r="AE42" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF42" s="1">
+        <f t="shared" si="10"/>
+        <v>175.09031999999999</v>
+      </c>
       <c r="AG42" s="1"/>
       <c r="AH42" s="1"/>
       <c r="AI42" s="1"/>
@@ -5487,7 +5837,7 @@
         <v>155</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-19</v>
       </c>
       <c r="M43" s="1"/>
@@ -5499,19 +5849,19 @@
         <v>69.160000000000025</v>
       </c>
       <c r="Q43" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>27.2</v>
       </c>
       <c r="R43" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>27.239999999999952</v>
       </c>
       <c r="S43" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T43" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10.998529411764707</v>
       </c>
       <c r="U43" s="1">
@@ -5537,12 +5887,21 @@
       </c>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="AD43" s="1"/>
-      <c r="AE43" s="1"/>
-      <c r="AF43" s="1"/>
+      <c r="AD43" s="1">
+        <f t="shared" si="8"/>
+        <v>10.88</v>
+      </c>
+      <c r="AE43" s="1">
+        <f t="shared" si="9"/>
+        <v>77.2</v>
+      </c>
+      <c r="AF43" s="1">
+        <f t="shared" si="10"/>
+        <v>27.664000000000012</v>
+      </c>
       <c r="AG43" s="1"/>
       <c r="AH43" s="1"/>
       <c r="AI43" s="1"/>
@@ -5592,7 +5951,7 @@
         <v>127</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-5</v>
       </c>
       <c r="M44" s="1"/>
@@ -5602,18 +5961,18 @@
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24.4</v>
       </c>
       <c r="R44" s="5"/>
       <c r="S44" s="1">
-        <f t="shared" si="4"/>
-        <v>14.39877049180328</v>
-      </c>
-      <c r="T44" s="1">
         <f t="shared" si="5"/>
         <v>14.39877049180328</v>
       </c>
+      <c r="T44" s="1">
+        <f t="shared" si="6"/>
+        <v>14.39877049180328</v>
+      </c>
       <c r="U44" s="1">
         <v>27.8</v>
       </c>
@@ -5637,12 +5996,21 @@
       </c>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD44" s="1"/>
-      <c r="AE44" s="1"/>
-      <c r="AF44" s="1"/>
+      <c r="AD44" s="1">
+        <f t="shared" si="8"/>
+        <v>9.76</v>
+      </c>
+      <c r="AE44" s="1">
+        <f t="shared" si="9"/>
+        <v>106.13200000000001</v>
+      </c>
+      <c r="AF44" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG44" s="1"/>
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
@@ -5692,7 +6060,7 @@
         <v>84.8</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-13.616</v>
       </c>
       <c r="M45" s="1"/>
@@ -5704,19 +6072,19 @@
         <v>108.49267999999999</v>
       </c>
       <c r="Q45" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14.236799999999999</v>
       </c>
       <c r="R45" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>55.305919999999979</v>
       </c>
       <c r="S45" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.999999999999998</v>
       </c>
       <c r="T45" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.1152843335581029</v>
       </c>
       <c r="U45" s="1">
@@ -5742,12 +6110,21 @@
       </c>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>55</v>
       </c>
-      <c r="AD45" s="1"/>
-      <c r="AE45" s="1"/>
-      <c r="AF45" s="1"/>
+      <c r="AD45" s="1">
+        <f t="shared" si="8"/>
+        <v>14.236799999999999</v>
+      </c>
+      <c r="AE45" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF45" s="1">
+        <f t="shared" si="10"/>
+        <v>108.49267999999999</v>
+      </c>
       <c r="AG45" s="1"/>
       <c r="AH45" s="1"/>
       <c r="AI45" s="1"/>
@@ -5797,7 +6174,7 @@
         <v>136.4</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-11.445000000000007</v>
       </c>
       <c r="M46" s="1"/>
@@ -5809,19 +6186,19 @@
         <v>157.36224000000001</v>
       </c>
       <c r="Q46" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24.991</v>
       </c>
       <c r="R46" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>85.098759999999984</v>
       </c>
       <c r="S46" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T46" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.5948237365451572</v>
       </c>
       <c r="U46" s="1">
@@ -5847,12 +6224,21 @@
       </c>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>85</v>
       </c>
-      <c r="AD46" s="1"/>
-      <c r="AE46" s="1"/>
-      <c r="AF46" s="1"/>
+      <c r="AD46" s="1">
+        <f t="shared" si="8"/>
+        <v>24.991</v>
+      </c>
+      <c r="AE46" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF46" s="1">
+        <f t="shared" si="10"/>
+        <v>157.36224000000001</v>
+      </c>
       <c r="AG46" s="1"/>
       <c r="AH46" s="1"/>
       <c r="AI46" s="1"/>
@@ -5902,7 +6288,7 @@
         <v>395</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-9</v>
       </c>
       <c r="M47" s="1"/>
@@ -5914,19 +6300,19 @@
         <v>348.33599999999979</v>
       </c>
       <c r="Q47" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>77.2</v>
       </c>
       <c r="R47" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>178.06400000000031</v>
       </c>
       <c r="S47" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T47" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.6934715025906701</v>
       </c>
       <c r="U47" s="1">
@@ -5952,12 +6338,21 @@
       </c>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>62</v>
       </c>
-      <c r="AD47" s="1"/>
-      <c r="AE47" s="1"/>
-      <c r="AF47" s="1"/>
+      <c r="AD47" s="1">
+        <f t="shared" si="8"/>
+        <v>27.02</v>
+      </c>
+      <c r="AE47" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF47" s="1">
+        <f t="shared" si="10"/>
+        <v>121.91759999999992</v>
+      </c>
       <c r="AG47" s="1"/>
       <c r="AH47" s="1"/>
       <c r="AI47" s="1"/>
@@ -6007,7 +6402,7 @@
         <v>234</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-91</v>
       </c>
       <c r="M48" s="1"/>
@@ -6017,18 +6412,18 @@
       </c>
       <c r="P48" s="1"/>
       <c r="Q48" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28.6</v>
       </c>
       <c r="R48" s="5"/>
       <c r="S48" s="1">
-        <f t="shared" si="4"/>
-        <v>16.118881118881117</v>
-      </c>
-      <c r="T48" s="1">
         <f t="shared" si="5"/>
         <v>16.118881118881117</v>
       </c>
+      <c r="T48" s="1">
+        <f t="shared" si="6"/>
+        <v>16.118881118881117</v>
+      </c>
       <c r="U48" s="1">
         <v>26.6</v>
       </c>
@@ -6052,12 +6447,21 @@
       </c>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD48" s="1"/>
-      <c r="AE48" s="1"/>
-      <c r="AF48" s="1"/>
+      <c r="AD48" s="1">
+        <f t="shared" si="8"/>
+        <v>11.440000000000001</v>
+      </c>
+      <c r="AE48" s="1">
+        <f t="shared" si="9"/>
+        <v>160</v>
+      </c>
+      <c r="AF48" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG48" s="1"/>
       <c r="AH48" s="1"/>
       <c r="AI48" s="1"/>
@@ -6107,7 +6511,7 @@
         <v>40.299999999999997</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-7.9799999999999969</v>
       </c>
       <c r="M49" s="1"/>
@@ -6119,18 +6523,18 @@
         <v>72.656800000000004</v>
       </c>
       <c r="Q49" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.4640000000000004</v>
       </c>
       <c r="R49" s="5"/>
       <c r="S49" s="1">
-        <f t="shared" si="4"/>
-        <v>14.608292079207919</v>
-      </c>
-      <c r="T49" s="1">
         <f t="shared" si="5"/>
         <v>14.608292079207919</v>
       </c>
+      <c r="T49" s="1">
+        <f t="shared" si="6"/>
+        <v>14.608292079207919</v>
+      </c>
       <c r="U49" s="1">
         <v>7.74</v>
       </c>
@@ -6154,12 +6558,21 @@
       </c>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD49" s="1"/>
-      <c r="AE49" s="1"/>
-      <c r="AF49" s="1"/>
+      <c r="AD49" s="1">
+        <f t="shared" si="8"/>
+        <v>6.4640000000000004</v>
+      </c>
+      <c r="AE49" s="1">
+        <f t="shared" si="9"/>
+        <v>23.109200000000001</v>
+      </c>
+      <c r="AF49" s="1">
+        <f t="shared" si="10"/>
+        <v>72.656800000000004</v>
+      </c>
       <c r="AG49" s="1"/>
       <c r="AH49" s="1"/>
       <c r="AI49" s="1"/>
@@ -6209,7 +6622,7 @@
         <v>137.15</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>9.9279999999999973</v>
       </c>
       <c r="M50" s="1"/>
@@ -6221,19 +6634,19 @@
         <v>177.90880000000001</v>
       </c>
       <c r="Q50" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29.415600000000001</v>
       </c>
       <c r="R50" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>77.971400000000017</v>
       </c>
       <c r="S50" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T50" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.3493180489264205</v>
       </c>
       <c r="U50" s="1">
@@ -6259,12 +6672,21 @@
       </c>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>78</v>
       </c>
-      <c r="AD50" s="1"/>
-      <c r="AE50" s="1"/>
-      <c r="AF50" s="1"/>
+      <c r="AD50" s="1">
+        <f t="shared" si="8"/>
+        <v>29.415600000000001</v>
+      </c>
+      <c r="AE50" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF50" s="1">
+        <f t="shared" si="10"/>
+        <v>177.90880000000001</v>
+      </c>
       <c r="AG50" s="1"/>
       <c r="AH50" s="1"/>
       <c r="AI50" s="1"/>
@@ -6308,7 +6730,7 @@
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
       <c r="L51" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M51" s="9"/>
@@ -6318,18 +6740,18 @@
       </c>
       <c r="P51" s="9"/>
       <c r="Q51" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R51" s="11"/>
       <c r="S51" s="9" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T51" s="9" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="T51" s="9" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="U51" s="9">
         <v>0</v>
       </c>
@@ -6353,12 +6775,21 @@
       </c>
       <c r="AB51" s="9"/>
       <c r="AC51" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD51" s="1"/>
-      <c r="AE51" s="1"/>
-      <c r="AF51" s="1"/>
+      <c r="AD51" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE51" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF51" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG51" s="1"/>
       <c r="AH51" s="1"/>
       <c r="AI51" s="1"/>
@@ -6404,7 +6835,7 @@
         <v>16.8</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-16.8</v>
       </c>
       <c r="M52" s="1"/>
@@ -6414,18 +6845,18 @@
       </c>
       <c r="P52" s="1"/>
       <c r="Q52" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R52" s="5"/>
       <c r="S52" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T52" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="T52" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="U52" s="1">
         <v>0</v>
       </c>
@@ -6449,12 +6880,21 @@
       </c>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD52" s="1"/>
-      <c r="AE52" s="1"/>
-      <c r="AF52" s="1"/>
+      <c r="AD52" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE52" s="1">
+        <f t="shared" si="9"/>
+        <v>50</v>
+      </c>
+      <c r="AF52" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG52" s="1"/>
       <c r="AH52" s="1"/>
       <c r="AI52" s="1"/>
@@ -6504,7 +6944,7 @@
         <v>137</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-50</v>
       </c>
       <c r="M53" s="1"/>
@@ -6514,18 +6954,18 @@
       </c>
       <c r="P53" s="1"/>
       <c r="Q53" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.399999999999999</v>
       </c>
       <c r="R53" s="5"/>
       <c r="S53" s="1">
-        <f t="shared" si="4"/>
-        <v>20.459770114942529</v>
-      </c>
-      <c r="T53" s="1">
         <f t="shared" si="5"/>
         <v>20.459770114942529</v>
       </c>
+      <c r="T53" s="1">
+        <f t="shared" si="6"/>
+        <v>20.459770114942529</v>
+      </c>
       <c r="U53" s="1">
         <v>23</v>
       </c>
@@ -6549,12 +6989,21 @@
       </c>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD53" s="1"/>
-      <c r="AE53" s="1"/>
-      <c r="AF53" s="1"/>
+      <c r="AD53" s="1">
+        <f t="shared" si="8"/>
+        <v>7.8299999999999992</v>
+      </c>
+      <c r="AE53" s="1">
+        <f t="shared" si="9"/>
+        <v>112.5</v>
+      </c>
+      <c r="AF53" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG53" s="1"/>
       <c r="AH53" s="1"/>
       <c r="AI53" s="1"/>
@@ -6604,7 +7053,7 @@
         <v>232</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-29</v>
       </c>
       <c r="M54" s="1"/>
@@ -6616,19 +7065,19 @@
         <v>97.981999999999957</v>
       </c>
       <c r="Q54" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>40.6</v>
       </c>
       <c r="R54" s="5">
-        <f t="shared" ref="R54:R91" si="10">12*Q54-P54-O54-F54</f>
+        <f t="shared" ref="R54:R91" si="14">12*Q54-P54-O54-F54</f>
         <v>84.218000000000075</v>
       </c>
       <c r="S54" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T54" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.9256650246305416</v>
       </c>
       <c r="U54" s="1">
@@ -6654,12 +7103,21 @@
       </c>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>38</v>
       </c>
-      <c r="AD54" s="1"/>
-      <c r="AE54" s="1"/>
-      <c r="AF54" s="1"/>
+      <c r="AD54" s="1">
+        <f t="shared" si="8"/>
+        <v>18.27</v>
+      </c>
+      <c r="AE54" s="1">
+        <f t="shared" si="9"/>
+        <v>67.5</v>
+      </c>
+      <c r="AF54" s="1">
+        <f t="shared" si="10"/>
+        <v>44.091899999999981</v>
+      </c>
       <c r="AG54" s="1"/>
       <c r="AH54" s="1"/>
       <c r="AI54" s="1"/>
@@ -6707,7 +7165,7 @@
         <v>93</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-34</v>
       </c>
       <c r="M55" s="1"/>
@@ -6719,18 +7177,18 @@
         <v>186.2</v>
       </c>
       <c r="Q55" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11.8</v>
       </c>
       <c r="R55" s="5"/>
       <c r="S55" s="1">
-        <f t="shared" si="4"/>
-        <v>25.474576271186439</v>
-      </c>
-      <c r="T55" s="1">
         <f t="shared" si="5"/>
         <v>25.474576271186439</v>
       </c>
+      <c r="T55" s="1">
+        <f t="shared" si="6"/>
+        <v>25.474576271186439</v>
+      </c>
       <c r="U55" s="1">
         <v>23</v>
       </c>
@@ -6754,12 +7212,21 @@
       </c>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD55" s="1"/>
-      <c r="AE55" s="1"/>
-      <c r="AF55" s="1"/>
+      <c r="AD55" s="1">
+        <f t="shared" si="8"/>
+        <v>4.7200000000000006</v>
+      </c>
+      <c r="AE55" s="1">
+        <f t="shared" si="9"/>
+        <v>45.760000000000005</v>
+      </c>
+      <c r="AF55" s="1">
+        <f t="shared" si="10"/>
+        <v>74.48</v>
+      </c>
       <c r="AG55" s="1"/>
       <c r="AH55" s="1"/>
       <c r="AI55" s="1"/>
@@ -6809,7 +7276,7 @@
         <v>122</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-92</v>
       </c>
       <c r="M56" s="1"/>
@@ -6819,19 +7286,19 @@
       </c>
       <c r="P56" s="1"/>
       <c r="Q56" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="R56" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>5.4320000000000022</v>
       </c>
       <c r="S56" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T56" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.094666666666667</v>
       </c>
       <c r="U56" s="1">
@@ -6857,12 +7324,21 @@
       </c>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AD56" s="1"/>
-      <c r="AE56" s="1"/>
-      <c r="AF56" s="1"/>
+      <c r="AD56" s="1">
+        <f t="shared" si="8"/>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="AE56" s="1">
+        <f t="shared" si="9"/>
+        <v>8.6272000000000002</v>
+      </c>
+      <c r="AF56" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG56" s="1"/>
       <c r="AH56" s="1"/>
       <c r="AI56" s="1"/>
@@ -6912,7 +7388,7 @@
         <v>143.55000000000001</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>7.1079999999999757</v>
       </c>
       <c r="M57" s="1"/>
@@ -6924,19 +7400,19 @@
         <v>243.05604</v>
       </c>
       <c r="Q57" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>30.131599999999999</v>
       </c>
       <c r="R57" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>56.80016000000002</v>
       </c>
       <c r="S57" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12.000000000000002</v>
       </c>
       <c r="T57" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10.114930504852049</v>
       </c>
       <c r="U57" s="1">
@@ -6962,12 +7438,21 @@
       </c>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>57</v>
       </c>
-      <c r="AD57" s="1"/>
-      <c r="AE57" s="1"/>
-      <c r="AF57" s="1"/>
+      <c r="AD57" s="1">
+        <f t="shared" si="8"/>
+        <v>30.131599999999999</v>
+      </c>
+      <c r="AE57" s="1">
+        <f t="shared" si="9"/>
+        <v>50</v>
+      </c>
+      <c r="AF57" s="1">
+        <f t="shared" si="10"/>
+        <v>243.05604</v>
+      </c>
       <c r="AG57" s="1"/>
       <c r="AH57" s="1"/>
       <c r="AI57" s="1"/>
@@ -7017,7 +7502,7 @@
         <v>194</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="M58" s="1"/>
@@ -7029,18 +7514,18 @@
         <v>307.47000000000003</v>
       </c>
       <c r="Q58" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>45</v>
       </c>
       <c r="R58" s="5"/>
       <c r="S58" s="1">
-        <f t="shared" si="4"/>
-        <v>15.966000000000001</v>
-      </c>
-      <c r="T58" s="1">
         <f t="shared" si="5"/>
         <v>15.966000000000001</v>
       </c>
+      <c r="T58" s="1">
+        <f t="shared" si="6"/>
+        <v>15.966000000000001</v>
+      </c>
       <c r="U58" s="1">
         <v>59.4</v>
       </c>
@@ -7064,12 +7549,21 @@
       </c>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD58" s="1"/>
-      <c r="AE58" s="1"/>
-      <c r="AF58" s="1"/>
+      <c r="AD58" s="1">
+        <f t="shared" si="8"/>
+        <v>4.5</v>
+      </c>
+      <c r="AE58" s="1">
+        <f t="shared" si="9"/>
+        <v>38</v>
+      </c>
+      <c r="AF58" s="1">
+        <f t="shared" si="10"/>
+        <v>30.747000000000003</v>
+      </c>
       <c r="AG58" s="1"/>
       <c r="AH58" s="1"/>
       <c r="AI58" s="1"/>
@@ -7119,7 +7613,7 @@
         <v>85.1</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>18.231000000000009</v>
       </c>
       <c r="M59" s="1"/>
@@ -7129,19 +7623,19 @@
       </c>
       <c r="P59" s="1"/>
       <c r="Q59" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20.6662</v>
       </c>
       <c r="R59" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>31.758399999999984</v>
       </c>
       <c r="S59" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T59" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10.463268525418316</v>
       </c>
       <c r="U59" s="1">
@@ -7167,12 +7661,21 @@
       </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="AD59" s="1"/>
-      <c r="AE59" s="1"/>
-      <c r="AF59" s="1"/>
+      <c r="AD59" s="1">
+        <f t="shared" si="8"/>
+        <v>20.6662</v>
+      </c>
+      <c r="AE59" s="1">
+        <f t="shared" si="9"/>
+        <v>200</v>
+      </c>
+      <c r="AF59" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG59" s="1"/>
       <c r="AH59" s="1"/>
       <c r="AI59" s="1"/>
@@ -7222,7 +7725,7 @@
         <v>13.5</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-8.0960000000000001</v>
       </c>
       <c r="M60" s="1"/>
@@ -7232,18 +7735,18 @@
       </c>
       <c r="P60" s="1"/>
       <c r="Q60" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0808</v>
       </c>
       <c r="R60" s="5">
         <v>10</v>
       </c>
       <c r="S60" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>33.318662102146561</v>
       </c>
       <c r="T60" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>24.066256476683936</v>
       </c>
       <c r="U60" s="1">
@@ -7269,12 +7772,21 @@
       </c>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="AD60" s="1"/>
-      <c r="AE60" s="1"/>
-      <c r="AF60" s="1"/>
+      <c r="AD60" s="1">
+        <f t="shared" si="8"/>
+        <v>1.0808</v>
+      </c>
+      <c r="AE60" s="1">
+        <f t="shared" si="9"/>
+        <v>32.72381</v>
+      </c>
+      <c r="AF60" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG60" s="1"/>
       <c r="AH60" s="1"/>
       <c r="AI60" s="1"/>
@@ -7324,7 +7836,7 @@
         <v>194</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>57</v>
       </c>
       <c r="M61" s="1"/>
@@ -7336,19 +7848,19 @@
         <v>282.60000000000002</v>
       </c>
       <c r="Q61" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>50.2</v>
       </c>
       <c r="R61" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>21.800000000000068</v>
       </c>
       <c r="S61" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12.000000000000002</v>
       </c>
       <c r="T61" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.565737051792828</v>
       </c>
       <c r="U61" s="1">
@@ -7374,12 +7886,21 @@
       </c>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="AD61" s="1"/>
-      <c r="AE61" s="1"/>
-      <c r="AF61" s="1"/>
+      <c r="AD61" s="1">
+        <f t="shared" si="8"/>
+        <v>5.0200000000000005</v>
+      </c>
+      <c r="AE61" s="1">
+        <f t="shared" si="9"/>
+        <v>30.400000000000002</v>
+      </c>
+      <c r="AF61" s="1">
+        <f t="shared" si="10"/>
+        <v>28.260000000000005</v>
+      </c>
       <c r="AG61" s="1"/>
       <c r="AH61" s="1"/>
       <c r="AI61" s="1"/>
@@ -7429,7 +7950,7 @@
         <v>26</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-11</v>
       </c>
       <c r="M62" s="1"/>
@@ -7439,18 +7960,18 @@
       </c>
       <c r="P62" s="1"/>
       <c r="Q62" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="R62" s="5"/>
       <c r="S62" s="1">
-        <f t="shared" si="4"/>
-        <v>11.733333333333334</v>
-      </c>
-      <c r="T62" s="1">
         <f t="shared" si="5"/>
         <v>11.733333333333334</v>
       </c>
+      <c r="T62" s="1">
+        <f t="shared" si="6"/>
+        <v>11.733333333333334</v>
+      </c>
       <c r="U62" s="1">
         <v>2.2000000000000002</v>
       </c>
@@ -7474,12 +7995,21 @@
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD62" s="1"/>
-      <c r="AE62" s="1"/>
-      <c r="AF62" s="1"/>
+      <c r="AD62" s="1">
+        <f t="shared" si="8"/>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="AE62" s="1">
+        <f t="shared" si="9"/>
+        <v>13.680000000000001</v>
+      </c>
+      <c r="AF62" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG62" s="1"/>
       <c r="AH62" s="1"/>
       <c r="AI62" s="1"/>
@@ -7525,7 +8055,7 @@
         <v>9.9</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-9.9</v>
       </c>
       <c r="M63" s="1"/>
@@ -7535,20 +8065,20 @@
       </c>
       <c r="P63" s="1"/>
       <c r="Q63" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R63" s="5">
         <v>10</v>
       </c>
       <c r="S63" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T63" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="T63" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="U63" s="1">
         <v>0</v>
       </c>
@@ -7572,12 +8102,21 @@
       </c>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="AD63" s="1"/>
-      <c r="AE63" s="1"/>
-      <c r="AF63" s="1"/>
+      <c r="AD63" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE63" s="1">
+        <f t="shared" si="9"/>
+        <v>22.078199999999999</v>
+      </c>
+      <c r="AF63" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG63" s="1"/>
       <c r="AH63" s="1"/>
       <c r="AI63" s="1"/>
@@ -7625,7 +8164,7 @@
         <v>33.700000000000003</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-33.700000000000003</v>
       </c>
       <c r="M64" s="1"/>
@@ -7635,18 +8174,18 @@
       </c>
       <c r="P64" s="1"/>
       <c r="Q64" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R64" s="5"/>
       <c r="S64" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T64" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="T64" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="U64" s="1">
         <v>1.8466</v>
       </c>
@@ -7670,12 +8209,21 @@
       </c>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD64" s="1"/>
-      <c r="AE64" s="1"/>
-      <c r="AF64" s="1"/>
+      <c r="AD64" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE64" s="1">
+        <f t="shared" si="9"/>
+        <v>104.47726</v>
+      </c>
+      <c r="AF64" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG64" s="1"/>
       <c r="AH64" s="1"/>
       <c r="AI64" s="1"/>
@@ -7725,7 +8273,7 @@
         <v>573</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-25</v>
       </c>
       <c r="M65" s="1"/>
@@ -7737,7 +8285,7 @@
         <v>668.76</v>
       </c>
       <c r="Q65" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>109.6</v>
       </c>
       <c r="R65" s="5">
@@ -7745,11 +8293,11 @@
         <v>161.83999999999992</v>
       </c>
       <c r="S65" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="T65" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.5233576642335773</v>
       </c>
       <c r="U65" s="1">
@@ -7775,12 +8323,21 @@
       </c>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>65</v>
       </c>
-      <c r="AD65" s="1"/>
-      <c r="AE65" s="1"/>
-      <c r="AF65" s="1"/>
+      <c r="AD65" s="1">
+        <f t="shared" si="8"/>
+        <v>43.84</v>
+      </c>
+      <c r="AE65" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF65" s="1">
+        <f t="shared" si="10"/>
+        <v>267.50400000000002</v>
+      </c>
       <c r="AG65" s="1"/>
       <c r="AH65" s="1"/>
       <c r="AI65" s="1"/>
@@ -7830,7 +8387,7 @@
         <v>413</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-55</v>
       </c>
       <c r="M66" s="1"/>
@@ -7842,18 +8399,18 @@
         <v>628.7199999999998</v>
       </c>
       <c r="Q66" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>71.599999999999994</v>
       </c>
       <c r="R66" s="5"/>
       <c r="S66" s="1">
-        <f t="shared" si="4"/>
-        <v>12.40391061452514</v>
-      </c>
-      <c r="T66" s="1">
         <f t="shared" si="5"/>
         <v>12.40391061452514</v>
       </c>
+      <c r="T66" s="1">
+        <f t="shared" si="6"/>
+        <v>12.40391061452514</v>
+      </c>
       <c r="U66" s="1">
         <v>76.599999999999994</v>
       </c>
@@ -7877,12 +8434,21 @@
       </c>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD66" s="1"/>
-      <c r="AE66" s="1"/>
-      <c r="AF66" s="1"/>
+      <c r="AD66" s="1">
+        <f t="shared" si="8"/>
+        <v>28.64</v>
+      </c>
+      <c r="AE66" s="1">
+        <f t="shared" si="9"/>
+        <v>108.16000000000004</v>
+      </c>
+      <c r="AF66" s="1">
+        <f t="shared" si="10"/>
+        <v>251.48799999999994</v>
+      </c>
       <c r="AG66" s="1"/>
       <c r="AH66" s="1"/>
       <c r="AI66" s="1"/>
@@ -7932,7 +8498,7 @@
         <v>159.80000000000001</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-106.655</v>
       </c>
       <c r="M67" s="1"/>
@@ -7942,18 +8508,18 @@
       </c>
       <c r="P67" s="1"/>
       <c r="Q67" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10.629000000000001</v>
       </c>
       <c r="R67" s="5"/>
       <c r="S67" s="1">
-        <f t="shared" si="4"/>
-        <v>26.539953147050529</v>
-      </c>
-      <c r="T67" s="1">
         <f t="shared" si="5"/>
         <v>26.539953147050529</v>
       </c>
+      <c r="T67" s="1">
+        <f t="shared" si="6"/>
+        <v>26.539953147050529</v>
+      </c>
       <c r="U67" s="1">
         <v>20.083200000000001</v>
       </c>
@@ -7977,12 +8543,21 @@
       </c>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD67" s="1"/>
-      <c r="AE67" s="1"/>
-      <c r="AF67" s="1"/>
+      <c r="AD67" s="1">
+        <f t="shared" si="8"/>
+        <v>10.629000000000001</v>
+      </c>
+      <c r="AE67" s="1">
+        <f t="shared" si="9"/>
+        <v>198.27116200000009</v>
+      </c>
+      <c r="AF67" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="AG67" s="1"/>
       <c r="AH67" s="1"/>
       <c r="AI67" s="1"/>
@@ -8032,7 +8607,7 @@
         <v>144.30000000000001</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-28.622000000000014</v>
       </c>
       <c r="M68" s="1"/>
@@ -8044,18 +8619,18 @@
         <v>178.69411999999991</v>
       </c>
       <c r="Q68" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23.1356</v>
       </c>
       <c r="R68" s="5"/>
       <c r="S68" s="1">
-        <f t="shared" si="4"/>
-        <v>16.531624422967205</v>
-      </c>
-      <c r="T68" s="1">
         <f t="shared" si="5"/>
         <v>16.531624422967205</v>
       </c>
+      <c r="T68" s="1">
+        <f t="shared" si="6"/>
+        <v>16.531624422967205</v>
+      </c>
       <c r="U68" s="1">
         <v>31.2576</v>
       </c>
@@ -8079,12 +8654,21 @@
       </c>
       <c r="AB68" s="1"/>
       <c r="AC68" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD68" s="1"/>
-      <c r="AE68" s="1"/>
-      <c r="AF68" s="1"/>
+      <c r="AD68" s="1">
+        <f t="shared" si="8"/>
+        <v>23.1356</v>
+      </c>
+      <c r="AE68" s="1">
+        <f t="shared" si="9"/>
+        <v>161.86093000000011</v>
+      </c>
+      <c r="AF68" s="1">
+        <f t="shared" si="10"/>
+        <v>178.69411999999991</v>
+      </c>
       <c r="AG68" s="1"/>
       <c r="AH68" s="1"/>
       <c r="AI68" s="1"/>
@@ -8134,7 +8718,7 @@
         <v>496.81099999999998</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>62.142999999999972</v>
       </c>
       <c r="M69" s="1"/>
@@ -8146,19 +8730,19 @@
         <v>811.15199999999982</v>
       </c>
       <c r="Q69" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>111.79079999999999</v>
       </c>
       <c r="R69" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>275.89066999999994</v>
       </c>
       <c r="S69" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T69" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.5320807257842333</v>
       </c>
       <c r="U69" s="1">
@@ -8184,12 +8768,21 @@
       </c>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>276</v>
       </c>
-      <c r="AD69" s="1"/>
-      <c r="AE69" s="1"/>
-      <c r="AF69" s="1"/>
+      <c r="AD69" s="1">
+        <f t="shared" si="8"/>
+        <v>111.79079999999999</v>
+      </c>
+      <c r="AE69" s="1">
+        <f t="shared" si="9"/>
+        <v>65.331930000000114</v>
+      </c>
+      <c r="AF69" s="1">
+        <f t="shared" si="10"/>
+        <v>811.15199999999982</v>
+      </c>
       <c r="AG69" s="1"/>
       <c r="AH69" s="1"/>
       <c r="AI69" s="1"/>
@@ -8239,7 +8832,7 @@
         <v>162.30000000000001</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="11">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="15">E70-K70</f>
         <v>-72.52300000000001</v>
       </c>
       <c r="M70" s="1"/>
@@ -8251,18 +8844,18 @@
         <v>80.299000000000049</v>
       </c>
       <c r="Q70" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.955400000000001</v>
       </c>
       <c r="R70" s="5"/>
       <c r="S70" s="1">
-        <f t="shared" si="4"/>
-        <v>22.494878866524836</v>
-      </c>
-      <c r="T70" s="1">
         <f t="shared" si="5"/>
         <v>22.494878866524836</v>
       </c>
+      <c r="T70" s="1">
+        <f t="shared" si="6"/>
+        <v>22.494878866524836</v>
+      </c>
       <c r="U70" s="1">
         <v>33.378999999999998</v>
       </c>
@@ -8286,12 +8879,21 @@
       </c>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD70" s="1"/>
-      <c r="AE70" s="1"/>
-      <c r="AF70" s="1"/>
+      <c r="AD70" s="1">
+        <f t="shared" si="8"/>
+        <v>17.955400000000001</v>
+      </c>
+      <c r="AE70" s="1">
+        <f t="shared" si="9"/>
+        <v>278.57154800000001</v>
+      </c>
+      <c r="AF70" s="1">
+        <f t="shared" si="10"/>
+        <v>80.299000000000049</v>
+      </c>
       <c r="AG70" s="1"/>
       <c r="AH70" s="1"/>
       <c r="AI70" s="1"/>
@@ -8341,7 +8943,7 @@
         <v>17</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-3</v>
       </c>
       <c r="M71" s="1"/>
@@ -8351,19 +8953,19 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1">
-        <f t="shared" ref="Q71:Q114" si="12">E71/5</f>
+        <f t="shared" ref="Q71:Q114" si="16">E71/5</f>
         <v>2.8</v>
       </c>
       <c r="R71" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>18.599999999999994</v>
       </c>
       <c r="S71" s="1">
-        <f t="shared" ref="S71:S114" si="13">(F71+O71+P71+R71)/Q71</f>
+        <f t="shared" ref="S71:S114" si="17">(F71+O71+P71+R71)/Q71</f>
         <v>11.999999999999998</v>
       </c>
       <c r="T71" s="1">
-        <f t="shared" ref="T71:T114" si="14">(F71+O71+P71)/Q71</f>
+        <f t="shared" ref="T71:T114" si="18">(F71+O71+P71)/Q71</f>
         <v>5.3571428571428577</v>
       </c>
       <c r="U71" s="1">
@@ -8389,12 +8991,21 @@
       </c>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1">
-        <f t="shared" ref="AC71:AC114" si="15">ROUND(G71*R71,0)</f>
+        <f t="shared" ref="AC71:AC114" si="19">ROUND(G71*R71,0)</f>
         <v>11</v>
       </c>
-      <c r="AD71" s="1"/>
-      <c r="AE71" s="1"/>
-      <c r="AF71" s="1"/>
+      <c r="AD71" s="1">
+        <f t="shared" ref="AD71:AD114" si="20">Q71*G71</f>
+        <v>1.68</v>
+      </c>
+      <c r="AE71" s="1">
+        <f t="shared" ref="AE71:AE114" si="21">O71*G71</f>
+        <v>0</v>
+      </c>
+      <c r="AF71" s="1">
+        <f t="shared" ref="AF71:AF114" si="22">P71*G71</f>
+        <v>0</v>
+      </c>
       <c r="AG71" s="1"/>
       <c r="AH71" s="1"/>
       <c r="AI71" s="1"/>
@@ -8444,7 +9055,7 @@
         <v>281.2</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-52.557999999999993</v>
       </c>
       <c r="M72" s="1"/>
@@ -8454,19 +9065,19 @@
       </c>
       <c r="P72" s="1"/>
       <c r="Q72" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>45.728400000000001</v>
       </c>
       <c r="R72" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>265.12380000000002</v>
       </c>
       <c r="S72" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T72" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6.2022069436061615</v>
       </c>
       <c r="U72" s="1">
@@ -8492,12 +9103,21 @@
       </c>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>265</v>
       </c>
-      <c r="AD72" s="1"/>
-      <c r="AE72" s="1"/>
-      <c r="AF72" s="1"/>
+      <c r="AD72" s="1">
+        <f t="shared" si="20"/>
+        <v>45.728400000000001</v>
+      </c>
+      <c r="AE72" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF72" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG72" s="1"/>
       <c r="AH72" s="1"/>
       <c r="AI72" s="1"/>
@@ -8543,7 +9163,7 @@
         <v>49</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
       <c r="M73" s="1"/>
@@ -8555,16 +9175,16 @@
         <v>91.44</v>
       </c>
       <c r="Q73" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>12.6</v>
       </c>
       <c r="R73" s="5"/>
       <c r="S73" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>14.336507936507935</v>
       </c>
       <c r="T73" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>14.336507936507935</v>
       </c>
       <c r="U73" s="1">
@@ -8590,12 +9210,21 @@
       </c>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD73" s="1"/>
-      <c r="AE73" s="1"/>
-      <c r="AF73" s="1"/>
+      <c r="AD73" s="1">
+        <f t="shared" si="20"/>
+        <v>7.56</v>
+      </c>
+      <c r="AE73" s="1">
+        <f t="shared" si="21"/>
+        <v>53.519999999999989</v>
+      </c>
+      <c r="AF73" s="1">
+        <f t="shared" si="22"/>
+        <v>54.863999999999997</v>
+      </c>
       <c r="AG73" s="1"/>
       <c r="AH73" s="1"/>
       <c r="AI73" s="1"/>
@@ -8645,7 +9274,7 @@
         <v>136</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>10</v>
       </c>
       <c r="M74" s="1"/>
@@ -8657,19 +9286,19 @@
         <v>66.2</v>
       </c>
       <c r="Q74" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>29.2</v>
       </c>
       <c r="R74" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>120.19999999999999</v>
       </c>
       <c r="S74" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T74" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>7.8835616438356162</v>
       </c>
       <c r="U74" s="1">
@@ -8695,12 +9324,21 @@
       </c>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>48</v>
       </c>
-      <c r="AD74" s="1"/>
-      <c r="AE74" s="1"/>
-      <c r="AF74" s="1"/>
+      <c r="AD74" s="1">
+        <f t="shared" si="20"/>
+        <v>11.68</v>
+      </c>
+      <c r="AE74" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF74" s="1">
+        <f t="shared" si="22"/>
+        <v>26.480000000000004</v>
+      </c>
       <c r="AG74" s="1"/>
       <c r="AH74" s="1"/>
       <c r="AI74" s="1"/>
@@ -8750,7 +9388,7 @@
         <v>205</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-4</v>
       </c>
       <c r="M75" s="1"/>
@@ -8762,7 +9400,7 @@
         <v>229.24</v>
       </c>
       <c r="Q75" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>40.200000000000003</v>
       </c>
       <c r="R75" s="5">
@@ -8770,11 +9408,11 @@
         <v>165.96000000000004</v>
       </c>
       <c r="S75" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="T75" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6.8716417910447758</v>
       </c>
       <c r="U75" s="1">
@@ -8800,12 +9438,21 @@
       </c>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>55</v>
       </c>
-      <c r="AD75" s="1"/>
-      <c r="AE75" s="1"/>
-      <c r="AF75" s="1"/>
+      <c r="AD75" s="1">
+        <f t="shared" si="20"/>
+        <v>13.266000000000002</v>
+      </c>
+      <c r="AE75" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF75" s="1">
+        <f t="shared" si="22"/>
+        <v>75.649200000000008</v>
+      </c>
       <c r="AG75" s="1"/>
       <c r="AH75" s="1"/>
       <c r="AI75" s="1"/>
@@ -8855,7 +9502,7 @@
         <v>99</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-24</v>
       </c>
       <c r="M76" s="1"/>
@@ -8865,19 +9512,19 @@
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="R76" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>79</v>
       </c>
       <c r="S76" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T76" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6.7333333333333334</v>
       </c>
       <c r="U76" s="1">
@@ -8903,12 +9550,21 @@
       </c>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>28</v>
       </c>
-      <c r="AD76" s="1"/>
-      <c r="AE76" s="1"/>
-      <c r="AF76" s="1"/>
+      <c r="AD76" s="1">
+        <f t="shared" si="20"/>
+        <v>5.25</v>
+      </c>
+      <c r="AE76" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF76" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG76" s="1"/>
       <c r="AH76" s="1"/>
       <c r="AI76" s="1"/>
@@ -8958,7 +9614,7 @@
         <v>198</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-36</v>
       </c>
       <c r="M77" s="1"/>
@@ -8970,16 +9626,16 @@
         <v>287.08240000000001</v>
       </c>
       <c r="Q77" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>32.4</v>
       </c>
       <c r="R77" s="5"/>
       <c r="S77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>16.148456790123458</v>
       </c>
       <c r="T77" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>16.148456790123458</v>
       </c>
       <c r="U77" s="1">
@@ -9005,12 +9661,21 @@
       </c>
       <c r="AB77" s="1"/>
       <c r="AC77" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD77" s="1"/>
-      <c r="AE77" s="1"/>
-      <c r="AF77" s="1"/>
+      <c r="AD77" s="1">
+        <f t="shared" si="20"/>
+        <v>11.988</v>
+      </c>
+      <c r="AE77" s="1">
+        <f t="shared" si="21"/>
+        <v>87.737212</v>
+      </c>
+      <c r="AF77" s="1">
+        <f t="shared" si="22"/>
+        <v>106.220488</v>
+      </c>
       <c r="AG77" s="1"/>
       <c r="AH77" s="1"/>
       <c r="AI77" s="1"/>
@@ -9058,7 +9723,7 @@
         <v>47</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-10</v>
       </c>
       <c r="M78" s="1"/>
@@ -9070,16 +9735,16 @@
         <v>59.839999999999989</v>
       </c>
       <c r="Q78" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>7.4</v>
       </c>
       <c r="R78" s="5"/>
       <c r="S78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>19.978378378378373</v>
       </c>
       <c r="T78" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>19.978378378378373</v>
       </c>
       <c r="U78" s="1">
@@ -9105,12 +9770,21 @@
       </c>
       <c r="AB78" s="1"/>
       <c r="AC78" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD78" s="1"/>
-      <c r="AE78" s="1"/>
-      <c r="AF78" s="1"/>
+      <c r="AD78" s="1">
+        <f t="shared" si="20"/>
+        <v>2.4420000000000002</v>
+      </c>
+      <c r="AE78" s="1">
+        <f t="shared" si="21"/>
+        <v>29.040000000000003</v>
+      </c>
+      <c r="AF78" s="1">
+        <f t="shared" si="22"/>
+        <v>19.747199999999996</v>
+      </c>
       <c r="AG78" s="1"/>
       <c r="AH78" s="1"/>
       <c r="AI78" s="1"/>
@@ -9160,7 +9834,7 @@
         <v>121</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-31</v>
       </c>
       <c r="M79" s="1"/>
@@ -9170,19 +9844,19 @@
       </c>
       <c r="P79" s="1"/>
       <c r="Q79" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>18</v>
       </c>
       <c r="R79" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>109</v>
       </c>
       <c r="S79" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T79" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5.9444444444444446</v>
       </c>
       <c r="U79" s="1">
@@ -9208,12 +9882,21 @@
       </c>
       <c r="AB79" s="1"/>
       <c r="AC79" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>44</v>
       </c>
-      <c r="AD79" s="1"/>
-      <c r="AE79" s="1"/>
-      <c r="AF79" s="1"/>
+      <c r="AD79" s="1">
+        <f t="shared" si="20"/>
+        <v>7.2</v>
+      </c>
+      <c r="AE79" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF79" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG79" s="1"/>
       <c r="AH79" s="1"/>
       <c r="AI79" s="1"/>
@@ -9263,7 +9946,7 @@
         <v>36</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-13</v>
       </c>
       <c r="M80" s="1"/>
@@ -9273,16 +9956,16 @@
       </c>
       <c r="P80" s="1"/>
       <c r="Q80" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="R80" s="5"/>
       <c r="S80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>28.695652173913047</v>
       </c>
       <c r="T80" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>28.695652173913047</v>
       </c>
       <c r="U80" s="1">
@@ -9308,12 +9991,21 @@
       </c>
       <c r="AB80" s="1"/>
       <c r="AC80" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD80" s="1"/>
-      <c r="AE80" s="1"/>
-      <c r="AF80" s="1"/>
+      <c r="AD80" s="1">
+        <f t="shared" si="20"/>
+        <v>1.6099999999999999</v>
+      </c>
+      <c r="AE80" s="1">
+        <f t="shared" si="21"/>
+        <v>35</v>
+      </c>
+      <c r="AF80" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG80" s="1"/>
       <c r="AH80" s="1"/>
       <c r="AI80" s="1"/>
@@ -9357,7 +10049,7 @@
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M81" s="1"/>
@@ -9367,16 +10059,16 @@
       </c>
       <c r="P81" s="1"/>
       <c r="Q81" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="R81" s="5"/>
       <c r="S81" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T81" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U81" s="1">
@@ -9402,12 +10094,21 @@
       </c>
       <c r="AB81" s="1"/>
       <c r="AC81" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD81" s="1"/>
-      <c r="AE81" s="1"/>
-      <c r="AF81" s="1"/>
+      <c r="AD81" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AE81" s="1">
+        <f t="shared" si="21"/>
+        <v>47.25</v>
+      </c>
+      <c r="AF81" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG81" s="1"/>
       <c r="AH81" s="1"/>
       <c r="AI81" s="1"/>
@@ -9457,7 +10158,7 @@
         <v>92</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-23</v>
       </c>
       <c r="M82" s="1"/>
@@ -9467,19 +10168,19 @@
       </c>
       <c r="P82" s="1"/>
       <c r="Q82" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>13.8</v>
       </c>
       <c r="R82" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="S82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12.000000000000002</v>
       </c>
       <c r="T82" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5.913043478260871</v>
       </c>
       <c r="U82" s="1">
@@ -9505,12 +10206,21 @@
       </c>
       <c r="AB82" s="1"/>
       <c r="AC82" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>34</v>
       </c>
-      <c r="AD82" s="1"/>
-      <c r="AE82" s="1"/>
-      <c r="AF82" s="1"/>
+      <c r="AD82" s="1">
+        <f t="shared" si="20"/>
+        <v>5.5200000000000005</v>
+      </c>
+      <c r="AE82" s="1">
+        <f t="shared" si="21"/>
+        <v>27.440000000000012</v>
+      </c>
+      <c r="AF82" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG82" s="1"/>
       <c r="AH82" s="1"/>
       <c r="AI82" s="1"/>
@@ -9558,7 +10268,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-5.4040000000000008</v>
       </c>
       <c r="M83" s="1"/>
@@ -9570,16 +10280,16 @@
         <v>14.337759999999999</v>
       </c>
       <c r="Q83" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>0.57919999999999994</v>
       </c>
       <c r="R83" s="5"/>
       <c r="S83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>50.029972375690612</v>
       </c>
       <c r="T83" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>50.029972375690612</v>
       </c>
       <c r="U83" s="1">
@@ -9605,12 +10315,21 @@
       </c>
       <c r="AB83" s="1"/>
       <c r="AC83" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD83" s="1"/>
-      <c r="AE83" s="1"/>
-      <c r="AF83" s="1"/>
+      <c r="AD83" s="1">
+        <f t="shared" si="20"/>
+        <v>0.57919999999999994</v>
+      </c>
+      <c r="AE83" s="1">
+        <f t="shared" si="21"/>
+        <v>11.912599999999999</v>
+      </c>
+      <c r="AF83" s="1">
+        <f t="shared" si="22"/>
+        <v>14.337759999999999</v>
+      </c>
       <c r="AG83" s="1"/>
       <c r="AH83" s="1"/>
       <c r="AI83" s="1"/>
@@ -9660,7 +10379,7 @@
         <v>283.66000000000003</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-28.674000000000035</v>
       </c>
       <c r="M84" s="1"/>
@@ -9672,16 +10391,16 @@
         <v>298.99789199999998</v>
       </c>
       <c r="Q84" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>50.997199999999999</v>
       </c>
       <c r="R84" s="5"/>
       <c r="S84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>15.399902190708508</v>
       </c>
       <c r="T84" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>15.399902190708508</v>
       </c>
       <c r="U84" s="1">
@@ -9707,12 +10426,21 @@
       </c>
       <c r="AB84" s="1"/>
       <c r="AC84" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD84" s="1"/>
-      <c r="AE84" s="1"/>
-      <c r="AF84" s="1"/>
+      <c r="AD84" s="1">
+        <f t="shared" si="20"/>
+        <v>50.997199999999999</v>
+      </c>
+      <c r="AE84" s="1">
+        <f t="shared" si="21"/>
+        <v>400</v>
+      </c>
+      <c r="AF84" s="1">
+        <f t="shared" si="22"/>
+        <v>298.99789199999998</v>
+      </c>
       <c r="AG84" s="1"/>
       <c r="AH84" s="1"/>
       <c r="AI84" s="1"/>
@@ -9762,7 +10490,7 @@
         <v>1672.5</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-317.81099999999992</v>
       </c>
       <c r="M85" s="1"/>
@@ -9774,19 +10502,19 @@
         <v>453.72905008000072</v>
       </c>
       <c r="Q85" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>270.93780000000004</v>
       </c>
       <c r="R85" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>1242.2139579999998</v>
       </c>
       <c r="S85" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>11.999999999999998</v>
       </c>
       <c r="T85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>7.4151323366470097</v>
       </c>
       <c r="U85" s="1">
@@ -9812,12 +10540,21 @@
       </c>
       <c r="AB85" s="1"/>
       <c r="AC85" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1242</v>
       </c>
-      <c r="AD85" s="1"/>
-      <c r="AE85" s="1"/>
-      <c r="AF85" s="1"/>
+      <c r="AD85" s="1">
+        <f t="shared" si="20"/>
+        <v>270.93780000000004</v>
+      </c>
+      <c r="AE85" s="1">
+        <f t="shared" si="21"/>
+        <v>969.46059191999962</v>
+      </c>
+      <c r="AF85" s="1">
+        <f t="shared" si="22"/>
+        <v>453.72905008000072</v>
+      </c>
       <c r="AG85" s="1"/>
       <c r="AH85" s="1"/>
       <c r="AI85" s="1"/>
@@ -9867,7 +10604,7 @@
         <v>2102.5</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-228.3889999999999</v>
       </c>
       <c r="M86" s="1"/>
@@ -9879,19 +10616,19 @@
         <v>1641.5546793599999</v>
       </c>
       <c r="Q86" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>374.82220000000001</v>
       </c>
       <c r="R86" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>1412.6137160000001</v>
       </c>
       <c r="S86" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>8.231243197441346</v>
       </c>
       <c r="U86" s="1">
@@ -9917,12 +10654,21 @@
       </c>
       <c r="AB86" s="1"/>
       <c r="AC86" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>1413</v>
       </c>
-      <c r="AD86" s="1"/>
-      <c r="AE86" s="1"/>
-      <c r="AF86" s="1"/>
+      <c r="AD86" s="1">
+        <f t="shared" si="20"/>
+        <v>374.82220000000001</v>
+      </c>
+      <c r="AE86" s="1">
+        <f t="shared" si="21"/>
+        <v>1003.17200464</v>
+      </c>
+      <c r="AF86" s="1">
+        <f t="shared" si="22"/>
+        <v>1641.5546793599999</v>
+      </c>
       <c r="AG86" s="1"/>
       <c r="AH86" s="1"/>
       <c r="AI86" s="1"/>
@@ -9972,7 +10718,7 @@
         <v>3466.2</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-430.72699999999986</v>
       </c>
       <c r="M87" s="1"/>
@@ -9984,19 +10730,19 @@
         <v>4242.5290860799996</v>
       </c>
       <c r="Q87" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>607.09460000000001</v>
       </c>
       <c r="R87" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>154.85404799999992</v>
       </c>
       <c r="S87" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>11.744926000000659</v>
       </c>
       <c r="U87" s="1">
@@ -10022,12 +10768,21 @@
       </c>
       <c r="AB87" s="1"/>
       <c r="AC87" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>155</v>
       </c>
-      <c r="AD87" s="1"/>
-      <c r="AE87" s="1"/>
-      <c r="AF87" s="1"/>
+      <c r="AD87" s="1">
+        <f t="shared" si="20"/>
+        <v>607.09460000000001</v>
+      </c>
+      <c r="AE87" s="1">
+        <f t="shared" si="21"/>
+        <v>1753.295065920001</v>
+      </c>
+      <c r="AF87" s="1">
+        <f t="shared" si="22"/>
+        <v>4242.5290860799996</v>
+      </c>
       <c r="AG87" s="1"/>
       <c r="AH87" s="1"/>
       <c r="AI87" s="1"/>
@@ -10077,7 +10832,7 @@
         <v>175</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-150</v>
       </c>
       <c r="M88" s="1"/>
@@ -10087,16 +10842,16 @@
       </c>
       <c r="P88" s="1"/>
       <c r="Q88" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="R88" s="5"/>
       <c r="S88" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>50.477600000000002</v>
       </c>
       <c r="T88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>50.477600000000002</v>
       </c>
       <c r="U88" s="1">
@@ -10122,12 +10877,21 @@
       </c>
       <c r="AB88" s="1"/>
       <c r="AC88" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD88" s="1"/>
-      <c r="AE88" s="1"/>
-      <c r="AF88" s="1"/>
+      <c r="AD88" s="1">
+        <f t="shared" si="20"/>
+        <v>1.5</v>
+      </c>
+      <c r="AE88" s="1">
+        <f t="shared" si="21"/>
+        <v>61.316400000000002</v>
+      </c>
+      <c r="AF88" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG88" s="1"/>
       <c r="AH88" s="1"/>
       <c r="AI88" s="1"/>
@@ -10177,7 +10941,7 @@
         <v>60</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-3</v>
       </c>
       <c r="M89" s="1"/>
@@ -10187,19 +10951,19 @@
       </c>
       <c r="P89" s="1"/>
       <c r="Q89" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>11.4</v>
       </c>
       <c r="R89" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>44.800000000000011</v>
       </c>
       <c r="S89" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>8.0701754385964914</v>
       </c>
       <c r="U89" s="1">
@@ -10225,12 +10989,21 @@
       </c>
       <c r="AB89" s="1"/>
       <c r="AC89" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="AD89" s="1"/>
-      <c r="AE89" s="1"/>
-      <c r="AF89" s="1"/>
+      <c r="AD89" s="1">
+        <f t="shared" si="20"/>
+        <v>0.79800000000000015</v>
+      </c>
+      <c r="AE89" s="1">
+        <f t="shared" si="21"/>
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="AF89" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG89" s="1"/>
       <c r="AH89" s="1"/>
       <c r="AI89" s="1"/>
@@ -10278,7 +11051,7 @@
         <v>64</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-2</v>
       </c>
       <c r="M90" s="1"/>
@@ -10290,19 +11063,19 @@
         <v>22.11999999999999</v>
       </c>
       <c r="Q90" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>12.4</v>
       </c>
       <c r="R90" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>99.680000000000021</v>
       </c>
       <c r="S90" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>3.9612903225806444</v>
       </c>
       <c r="U90" s="1">
@@ -10328,12 +11101,21 @@
       </c>
       <c r="AB90" s="1"/>
       <c r="AC90" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>7</v>
       </c>
-      <c r="AD90" s="1"/>
-      <c r="AE90" s="1"/>
-      <c r="AF90" s="1"/>
+      <c r="AD90" s="1">
+        <f t="shared" si="20"/>
+        <v>0.8680000000000001</v>
+      </c>
+      <c r="AE90" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF90" s="1">
+        <f t="shared" si="22"/>
+        <v>1.5483999999999996</v>
+      </c>
       <c r="AG90" s="1"/>
       <c r="AH90" s="1"/>
       <c r="AI90" s="1"/>
@@ -10383,7 +11165,7 @@
         <v>64</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-2</v>
       </c>
       <c r="M91" s="1"/>
@@ -10395,19 +11177,19 @@
         <v>58.8</v>
       </c>
       <c r="Q91" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>12.4</v>
       </c>
       <c r="R91" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>61.000000000000014</v>
       </c>
       <c r="S91" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>7.0806451612903221</v>
       </c>
       <c r="U91" s="1">
@@ -10433,12 +11215,21 @@
       </c>
       <c r="AB91" s="1"/>
       <c r="AC91" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>4</v>
       </c>
-      <c r="AD91" s="1"/>
-      <c r="AE91" s="1"/>
-      <c r="AF91" s="1"/>
+      <c r="AD91" s="1">
+        <f t="shared" si="20"/>
+        <v>0.8680000000000001</v>
+      </c>
+      <c r="AE91" s="1">
+        <f t="shared" si="21"/>
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="AF91" s="1">
+        <f t="shared" si="22"/>
+        <v>4.1160000000000005</v>
+      </c>
       <c r="AG91" s="1"/>
       <c r="AH91" s="1"/>
       <c r="AI91" s="1"/>
@@ -10488,7 +11279,7 @@
         <v>97</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="M92" s="1"/>
@@ -10500,7 +11291,7 @@
         <v>51</v>
       </c>
       <c r="Q92" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20.2</v>
       </c>
       <c r="R92" s="5">
@@ -10508,11 +11299,11 @@
         <v>155.19999999999999</v>
       </c>
       <c r="S92" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="T92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>3.3168316831683171</v>
       </c>
       <c r="U92" s="1">
@@ -10538,12 +11329,21 @@
       </c>
       <c r="AB92" s="1"/>
       <c r="AC92" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>8</v>
       </c>
-      <c r="AD92" s="1"/>
-      <c r="AE92" s="1"/>
-      <c r="AF92" s="1"/>
+      <c r="AD92" s="1">
+        <f t="shared" si="20"/>
+        <v>1.01</v>
+      </c>
+      <c r="AE92" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF92" s="1">
+        <f t="shared" si="22"/>
+        <v>2.5500000000000003</v>
+      </c>
       <c r="AG92" s="1"/>
       <c r="AH92" s="1"/>
       <c r="AI92" s="1"/>
@@ -10593,7 +11393,7 @@
         <v>46</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-36</v>
       </c>
       <c r="M93" s="1"/>
@@ -10605,18 +11405,18 @@
         <v>32.188000000000002</v>
       </c>
       <c r="Q93" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="R93" s="12">
         <v>0</v>
       </c>
       <c r="S93" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>17.094000000000001</v>
       </c>
       <c r="T93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>17.094000000000001</v>
       </c>
       <c r="U93" s="1">
@@ -10644,12 +11444,21 @@
         <v>209</v>
       </c>
       <c r="AC93" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD93" s="1"/>
-      <c r="AE93" s="1"/>
-      <c r="AF93" s="1"/>
+      <c r="AD93" s="1">
+        <f t="shared" si="20"/>
+        <v>0.11</v>
+      </c>
+      <c r="AE93" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF93" s="1">
+        <f t="shared" si="22"/>
+        <v>1.7703400000000002</v>
+      </c>
       <c r="AG93" s="1"/>
       <c r="AH93" s="1"/>
       <c r="AI93" s="1"/>
@@ -10697,7 +11506,7 @@
         <v>63</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M94" s="1"/>
@@ -10709,18 +11518,18 @@
         <v>49.28</v>
       </c>
       <c r="Q94" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>12.6</v>
       </c>
       <c r="R94" s="12">
         <v>0</v>
       </c>
       <c r="S94" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>6.9111111111111123</v>
       </c>
       <c r="T94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6.9111111111111123</v>
       </c>
       <c r="U94" s="1">
@@ -10748,12 +11557,21 @@
         <v>209</v>
       </c>
       <c r="AC94" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD94" s="1"/>
-      <c r="AE94" s="1"/>
-      <c r="AF94" s="1"/>
+      <c r="AD94" s="1">
+        <f t="shared" si="20"/>
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="AE94" s="1">
+        <f t="shared" si="21"/>
+        <v>2.2440000000000007</v>
+      </c>
+      <c r="AF94" s="1">
+        <f t="shared" si="22"/>
+        <v>2.7103999999999999</v>
+      </c>
       <c r="AG94" s="1"/>
       <c r="AH94" s="1"/>
       <c r="AI94" s="1"/>
@@ -10803,7 +11621,7 @@
         <v>55.95</v>
       </c>
       <c r="L95" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>3.1119999999999948</v>
       </c>
       <c r="M95" s="9"/>
@@ -10813,16 +11631,16 @@
       </c>
       <c r="P95" s="9"/>
       <c r="Q95" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>11.8124</v>
       </c>
       <c r="R95" s="11"/>
       <c r="S95" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>11.11340625105821</v>
       </c>
       <c r="T95" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>11.11340625105821</v>
       </c>
       <c r="U95" s="9">
@@ -10850,12 +11668,21 @@
         <v>214</v>
       </c>
       <c r="AC95" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD95" s="1"/>
-      <c r="AE95" s="1"/>
-      <c r="AF95" s="1"/>
+      <c r="AD95" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AE95" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF95" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG95" s="1"/>
       <c r="AH95" s="1"/>
       <c r="AI95" s="1"/>
@@ -10903,7 +11730,7 @@
         <v>66</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-22</v>
       </c>
       <c r="M96" s="1"/>
@@ -10915,16 +11742,16 @@
         <v>69.84</v>
       </c>
       <c r="Q96" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="R96" s="5"/>
       <c r="S96" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>20.959090909090907</v>
       </c>
       <c r="T96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>20.959090909090907</v>
       </c>
       <c r="U96" s="1">
@@ -10950,12 +11777,21 @@
       </c>
       <c r="AB96" s="1"/>
       <c r="AC96" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD96" s="1"/>
-      <c r="AE96" s="1"/>
-      <c r="AF96" s="1"/>
+      <c r="AD96" s="1">
+        <f t="shared" si="20"/>
+        <v>0.70400000000000007</v>
+      </c>
+      <c r="AE96" s="1">
+        <f t="shared" si="21"/>
+        <v>8.2880000000000003</v>
+      </c>
+      <c r="AF96" s="1">
+        <f t="shared" si="22"/>
+        <v>5.5872000000000002</v>
+      </c>
       <c r="AG96" s="1"/>
       <c r="AH96" s="1"/>
       <c r="AI96" s="1"/>
@@ -11005,7 +11841,7 @@
         <v>89</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-3</v>
       </c>
       <c r="M97" s="1"/>
@@ -11015,19 +11851,19 @@
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>17.2</v>
       </c>
       <c r="R97" s="5">
-        <f t="shared" ref="R97:R114" si="16">12*Q97-P97-O97-F97</f>
+        <f t="shared" ref="R97:R114" si="23">12*Q97-P97-O97-F97</f>
         <v>74.399999999999977</v>
       </c>
       <c r="S97" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T97" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>7.6744186046511631</v>
       </c>
       <c r="U97" s="1">
@@ -11053,12 +11889,21 @@
       </c>
       <c r="AB97" s="1"/>
       <c r="AC97" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
-      <c r="AD97" s="1"/>
-      <c r="AE97" s="1"/>
-      <c r="AF97" s="1"/>
+      <c r="AD97" s="1">
+        <f t="shared" si="20"/>
+        <v>1.3759999999999999</v>
+      </c>
+      <c r="AE97" s="1">
+        <f t="shared" si="21"/>
+        <v>4</v>
+      </c>
+      <c r="AF97" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG97" s="1"/>
       <c r="AH97" s="1"/>
       <c r="AI97" s="1"/>
@@ -11108,7 +11953,7 @@
         <v>277.66300000000001</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-6.4519999999999982</v>
       </c>
       <c r="M98" s="1"/>
@@ -11120,19 +11965,19 @@
         <v>182.24948000000001</v>
       </c>
       <c r="Q98" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>54.242200000000004</v>
       </c>
       <c r="R98" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>191.99092000000007</v>
       </c>
       <c r="S98" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T98" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>8.4604879595591616</v>
       </c>
       <c r="U98" s="1">
@@ -11158,12 +12003,21 @@
       </c>
       <c r="AB98" s="1"/>
       <c r="AC98" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>192</v>
       </c>
-      <c r="AD98" s="1"/>
-      <c r="AE98" s="1"/>
-      <c r="AF98" s="1"/>
+      <c r="AD98" s="1">
+        <f t="shared" si="20"/>
+        <v>54.242200000000004</v>
+      </c>
+      <c r="AE98" s="1">
+        <f t="shared" si="21"/>
+        <v>100</v>
+      </c>
+      <c r="AF98" s="1">
+        <f t="shared" si="22"/>
+        <v>182.24948000000001</v>
+      </c>
       <c r="AG98" s="1"/>
       <c r="AH98" s="1"/>
       <c r="AI98" s="1"/>
@@ -11213,7 +12067,7 @@
         <v>270.60000000000002</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-3.1800000000000068</v>
       </c>
       <c r="M99" s="1"/>
@@ -11225,16 +12079,16 @@
         <v>305.87754447999998</v>
       </c>
       <c r="Q99" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>53.484000000000002</v>
       </c>
       <c r="R99" s="5"/>
       <c r="S99" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12.594252524119362</v>
       </c>
       <c r="T99" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>12.594252524119362</v>
       </c>
       <c r="U99" s="1">
@@ -11260,12 +12114,21 @@
       </c>
       <c r="AB99" s="1"/>
       <c r="AC99" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD99" s="1"/>
-      <c r="AE99" s="1"/>
-      <c r="AF99" s="1"/>
+      <c r="AD99" s="1">
+        <f t="shared" si="20"/>
+        <v>53.484000000000002</v>
+      </c>
+      <c r="AE99" s="1">
+        <f t="shared" si="21"/>
+        <v>257.18445752000002</v>
+      </c>
+      <c r="AF99" s="1">
+        <f t="shared" si="22"/>
+        <v>305.87754447999998</v>
+      </c>
       <c r="AG99" s="1"/>
       <c r="AH99" s="1"/>
       <c r="AI99" s="1"/>
@@ -11315,7 +12178,7 @@
         <v>288.39999999999998</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-20.906999999999982</v>
       </c>
       <c r="M100" s="1"/>
@@ -11327,16 +12190,16 @@
         <v>391.86171999999999</v>
       </c>
       <c r="Q100" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>53.498599999999996</v>
       </c>
       <c r="R100" s="5"/>
       <c r="S100" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12.900855723327341</v>
       </c>
       <c r="T100" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>12.900855723327341</v>
       </c>
       <c r="U100" s="1">
@@ -11362,12 +12225,21 @@
       </c>
       <c r="AB100" s="1"/>
       <c r="AC100" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD100" s="1"/>
-      <c r="AE100" s="1"/>
-      <c r="AF100" s="1"/>
+      <c r="AD100" s="1">
+        <f t="shared" si="20"/>
+        <v>53.498599999999996</v>
+      </c>
+      <c r="AE100" s="1">
+        <f t="shared" si="21"/>
+        <v>150</v>
+      </c>
+      <c r="AF100" s="1">
+        <f t="shared" si="22"/>
+        <v>391.86171999999999</v>
+      </c>
       <c r="AG100" s="1"/>
       <c r="AH100" s="1"/>
       <c r="AI100" s="1"/>
@@ -11415,7 +12287,7 @@
         <v>162</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-171</v>
       </c>
       <c r="M101" s="1"/>
@@ -11425,18 +12297,18 @@
       </c>
       <c r="P101" s="1"/>
       <c r="Q101" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>-1.8</v>
       </c>
       <c r="R101" s="5">
         <v>100</v>
       </c>
       <c r="S101" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-167.22222222222223</v>
       </c>
       <c r="T101" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-111.66666666666666</v>
       </c>
       <c r="U101" s="1">
@@ -11462,12 +12334,21 @@
       </c>
       <c r="AB101" s="1"/>
       <c r="AC101" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>28</v>
       </c>
-      <c r="AD101" s="1"/>
-      <c r="AE101" s="1"/>
-      <c r="AF101" s="1"/>
+      <c r="AD101" s="1">
+        <f t="shared" si="20"/>
+        <v>-0.50400000000000011</v>
+      </c>
+      <c r="AE101" s="1">
+        <f t="shared" si="21"/>
+        <v>56.000000000000007</v>
+      </c>
+      <c r="AF101" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG101" s="1"/>
       <c r="AH101" s="1"/>
       <c r="AI101" s="1"/>
@@ -11515,7 +12396,7 @@
         <v>213</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L114" si="17">E102-K102</f>
+        <f t="shared" ref="L102:L114" si="24">E102-K102</f>
         <v>0</v>
       </c>
       <c r="M102" s="1"/>
@@ -11527,7 +12408,7 @@
         <v>234.16</v>
       </c>
       <c r="Q102" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>42.6</v>
       </c>
       <c r="R102" s="5">
@@ -11535,11 +12416,11 @@
         <v>239.44000000000003</v>
       </c>
       <c r="S102" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="T102" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5.3793427230046946</v>
       </c>
       <c r="U102" s="1">
@@ -11565,12 +12446,21 @@
       </c>
       <c r="AB102" s="1"/>
       <c r="AC102" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>67</v>
       </c>
-      <c r="AD102" s="1"/>
-      <c r="AE102" s="1"/>
-      <c r="AF102" s="1"/>
+      <c r="AD102" s="1">
+        <f t="shared" si="20"/>
+        <v>11.928000000000001</v>
+      </c>
+      <c r="AE102" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF102" s="1">
+        <f t="shared" si="22"/>
+        <v>65.564800000000005</v>
+      </c>
       <c r="AG102" s="1"/>
       <c r="AH102" s="1"/>
       <c r="AI102" s="1"/>
@@ -11620,7 +12510,7 @@
         <v>230</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-16</v>
       </c>
       <c r="M103" s="1"/>
@@ -11632,19 +12522,19 @@
         <v>224.52</v>
       </c>
       <c r="Q103" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>42.8</v>
       </c>
       <c r="R103" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>83.079999999999927</v>
       </c>
       <c r="S103" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>11.999999999999998</v>
       </c>
       <c r="T103" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>10.058878504672897</v>
       </c>
       <c r="U103" s="1">
@@ -11670,12 +12560,21 @@
       </c>
       <c r="AB103" s="1"/>
       <c r="AC103" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>23</v>
       </c>
-      <c r="AD103" s="1"/>
-      <c r="AE103" s="1"/>
-      <c r="AF103" s="1"/>
+      <c r="AD103" s="1">
+        <f t="shared" si="20"/>
+        <v>11.984</v>
+      </c>
+      <c r="AE103" s="1">
+        <f t="shared" si="21"/>
+        <v>22.400000000000002</v>
+      </c>
+      <c r="AF103" s="1">
+        <f t="shared" si="22"/>
+        <v>62.865600000000008</v>
+      </c>
       <c r="AG103" s="1"/>
       <c r="AH103" s="1"/>
       <c r="AI103" s="1"/>
@@ -11725,7 +12624,7 @@
         <v>217.5</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-68.008999999999986</v>
       </c>
       <c r="M104" s="1"/>
@@ -11737,19 +12636,19 @@
         <v>234.91676000000001</v>
       </c>
       <c r="Q104" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>29.898200000000003</v>
       </c>
       <c r="R104" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>46.858640000000022</v>
       </c>
       <c r="S104" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T104" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>10.432727053802569</v>
       </c>
       <c r="U104" s="1">
@@ -11775,12 +12674,21 @@
       </c>
       <c r="AB104" s="1"/>
       <c r="AC104" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>47</v>
       </c>
-      <c r="AD104" s="1"/>
-      <c r="AE104" s="1"/>
-      <c r="AF104" s="1"/>
+      <c r="AD104" s="1">
+        <f t="shared" si="20"/>
+        <v>29.898200000000003</v>
+      </c>
+      <c r="AE104" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF104" s="1">
+        <f t="shared" si="22"/>
+        <v>234.91676000000001</v>
+      </c>
       <c r="AG104" s="1"/>
       <c r="AH104" s="1"/>
       <c r="AI104" s="1"/>
@@ -11830,7 +12738,7 @@
         <v>97.5</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-58.548000000000002</v>
       </c>
       <c r="M105" s="1"/>
@@ -11840,16 +12748,16 @@
       </c>
       <c r="P105" s="1"/>
       <c r="Q105" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>7.7904</v>
       </c>
       <c r="R105" s="5"/>
       <c r="S105" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>22.307228126925448</v>
       </c>
       <c r="T105" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>22.307228126925448</v>
       </c>
       <c r="U105" s="1">
@@ -11875,12 +12783,21 @@
       </c>
       <c r="AB105" s="1"/>
       <c r="AC105" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD105" s="1"/>
-      <c r="AE105" s="1"/>
-      <c r="AF105" s="1"/>
+      <c r="AD105" s="1">
+        <f t="shared" si="20"/>
+        <v>7.7904</v>
+      </c>
+      <c r="AE105" s="1">
+        <f t="shared" si="21"/>
+        <v>93.924229999999994</v>
+      </c>
+      <c r="AF105" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG105" s="1"/>
       <c r="AH105" s="1"/>
       <c r="AI105" s="1"/>
@@ -11924,7 +12841,7 @@
         <v>12.1</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-12.1</v>
       </c>
       <c r="M106" s="1"/>
@@ -11934,16 +12851,16 @@
       </c>
       <c r="P106" s="1"/>
       <c r="Q106" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="R106" s="5"/>
       <c r="S106" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T106" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U106" s="1">
@@ -11969,12 +12886,21 @@
       </c>
       <c r="AB106" s="1"/>
       <c r="AC106" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD106" s="1"/>
-      <c r="AE106" s="1"/>
-      <c r="AF106" s="1"/>
+      <c r="AD106" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AE106" s="1">
+        <f t="shared" si="21"/>
+        <v>150</v>
+      </c>
+      <c r="AF106" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG106" s="1"/>
       <c r="AH106" s="1"/>
       <c r="AI106" s="1"/>
@@ -12024,7 +12950,7 @@
         <v>108.574</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-4.9989999999999952</v>
       </c>
       <c r="M107" s="1"/>
@@ -12034,16 +12960,16 @@
       </c>
       <c r="P107" s="1"/>
       <c r="Q107" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20.715</v>
       </c>
       <c r="R107" s="5"/>
       <c r="S107" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>16.959594496741492</v>
       </c>
       <c r="T107" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>16.959594496741492</v>
       </c>
       <c r="U107" s="1">
@@ -12069,12 +12995,21 @@
       </c>
       <c r="AB107" s="1"/>
       <c r="AC107" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD107" s="1"/>
-      <c r="AE107" s="1"/>
-      <c r="AF107" s="1"/>
+      <c r="AD107" s="1">
+        <f t="shared" si="20"/>
+        <v>20.715</v>
+      </c>
+      <c r="AE107" s="1">
+        <f t="shared" si="21"/>
+        <v>200</v>
+      </c>
+      <c r="AF107" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG107" s="1"/>
       <c r="AH107" s="1"/>
       <c r="AI107" s="1"/>
@@ -12124,7 +13059,7 @@
         <v>71.900000000000006</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-7.5220000000000056</v>
       </c>
       <c r="M108" s="1"/>
@@ -12136,16 +13071,16 @@
         <v>133.88955999999999</v>
       </c>
       <c r="Q108" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>12.8756</v>
       </c>
       <c r="R108" s="5"/>
       <c r="S108" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>13.009006182236165</v>
       </c>
       <c r="T108" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>13.009006182236165</v>
       </c>
       <c r="U108" s="1">
@@ -12171,12 +13106,21 @@
       </c>
       <c r="AB108" s="1"/>
       <c r="AC108" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD108" s="1"/>
-      <c r="AE108" s="1"/>
-      <c r="AF108" s="1"/>
+      <c r="AD108" s="1">
+        <f t="shared" si="20"/>
+        <v>12.8756</v>
+      </c>
+      <c r="AE108" s="1">
+        <f t="shared" si="21"/>
+        <v>10.29219999999998</v>
+      </c>
+      <c r="AF108" s="1">
+        <f t="shared" si="22"/>
+        <v>133.88955999999999</v>
+      </c>
       <c r="AG108" s="1"/>
       <c r="AH108" s="1"/>
       <c r="AI108" s="1"/>
@@ -12222,7 +13166,7 @@
         <v>84.2</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-1.6400000000000006</v>
       </c>
       <c r="M109" s="1"/>
@@ -12232,16 +13176,16 @@
       </c>
       <c r="P109" s="1"/>
       <c r="Q109" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>16.512</v>
       </c>
       <c r="R109" s="5"/>
       <c r="S109" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>140.32580212693799</v>
       </c>
       <c r="T109" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>140.32580212693799</v>
       </c>
       <c r="U109" s="1">
@@ -12269,12 +13213,21 @@
         <v>239</v>
       </c>
       <c r="AC109" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD109" s="1"/>
-      <c r="AE109" s="1"/>
-      <c r="AF109" s="1"/>
+      <c r="AD109" s="1">
+        <f t="shared" si="20"/>
+        <v>16.512</v>
+      </c>
+      <c r="AE109" s="1">
+        <f t="shared" si="21"/>
+        <v>653.83964471999991</v>
+      </c>
+      <c r="AF109" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG109" s="1"/>
       <c r="AH109" s="1"/>
       <c r="AI109" s="1"/>
@@ -12324,7 +13277,7 @@
         <v>259</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-17</v>
       </c>
       <c r="M110" s="1"/>
@@ -12336,19 +13289,19 @@
         <v>355.52</v>
       </c>
       <c r="Q110" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>48.4</v>
       </c>
       <c r="R110" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>65.479999999999961</v>
       </c>
       <c r="S110" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="T110" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>10.647107438016528</v>
       </c>
       <c r="U110" s="1">
@@ -12374,12 +13327,21 @@
       </c>
       <c r="AB110" s="1"/>
       <c r="AC110" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>20</v>
       </c>
-      <c r="AD110" s="1"/>
-      <c r="AE110" s="1"/>
-      <c r="AF110" s="1"/>
+      <c r="AD110" s="1">
+        <f t="shared" si="20"/>
+        <v>14.52</v>
+      </c>
+      <c r="AE110" s="1">
+        <f t="shared" si="21"/>
+        <v>40.74</v>
+      </c>
+      <c r="AF110" s="1">
+        <f t="shared" si="22"/>
+        <v>106.65599999999999</v>
+      </c>
       <c r="AG110" s="1"/>
       <c r="AH110" s="1"/>
       <c r="AI110" s="1"/>
@@ -12429,7 +13391,7 @@
         <v>221</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-254</v>
       </c>
       <c r="M111" s="1"/>
@@ -12439,16 +13401,16 @@
       </c>
       <c r="P111" s="1"/>
       <c r="Q111" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>-6.6</v>
       </c>
       <c r="R111" s="5"/>
       <c r="S111" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>-24.242424242424242</v>
       </c>
       <c r="T111" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-24.242424242424242</v>
       </c>
       <c r="U111" s="1">
@@ -12476,12 +13438,21 @@
         <v>244</v>
       </c>
       <c r="AC111" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD111" s="1"/>
-      <c r="AE111" s="1"/>
-      <c r="AF111" s="1"/>
+      <c r="AD111" s="1">
+        <f t="shared" si="20"/>
+        <v>-1.9799999999999998</v>
+      </c>
+      <c r="AE111" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF111" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG111" s="1"/>
       <c r="AH111" s="1"/>
       <c r="AI111" s="1"/>
@@ -12527,7 +13498,7 @@
         <v>4</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-4</v>
       </c>
       <c r="M112" s="1"/>
@@ -12537,18 +13508,18 @@
       </c>
       <c r="P112" s="1"/>
       <c r="Q112" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="R112" s="5">
         <v>10</v>
       </c>
       <c r="S112" s="1" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T112" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U112" s="1">
@@ -12574,12 +13545,21 @@
       </c>
       <c r="AB112" s="1"/>
       <c r="AC112" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="AD112" s="1"/>
-      <c r="AE112" s="1"/>
-      <c r="AF112" s="1"/>
+      <c r="AD112" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AE112" s="1">
+        <f t="shared" si="21"/>
+        <v>14.59</v>
+      </c>
+      <c r="AF112" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AG112" s="1"/>
       <c r="AH112" s="1"/>
       <c r="AI112" s="1"/>
@@ -12629,7 +13609,7 @@
         <v>153</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-59</v>
       </c>
       <c r="M113" s="1"/>
@@ -12641,16 +13621,16 @@
         <v>91.279999999999973</v>
       </c>
       <c r="Q113" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>18.8</v>
       </c>
       <c r="R113" s="5"/>
       <c r="S113" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>13.206382978723402</v>
       </c>
       <c r="T113" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>13.206382978723402</v>
       </c>
       <c r="U113" s="1">
@@ -12676,12 +13656,21 @@
       </c>
       <c r="AB113" s="1"/>
       <c r="AC113" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AD113" s="1"/>
-      <c r="AE113" s="1"/>
-      <c r="AF113" s="1"/>
+      <c r="AD113" s="1">
+        <f t="shared" si="20"/>
+        <v>5.64</v>
+      </c>
+      <c r="AE113" s="1">
+        <f t="shared" si="21"/>
+        <v>48</v>
+      </c>
+      <c r="AF113" s="1">
+        <f t="shared" si="22"/>
+        <v>27.38399999999999</v>
+      </c>
       <c r="AG113" s="1"/>
       <c r="AH113" s="1"/>
       <c r="AI113" s="1"/>
@@ -12731,7 +13720,7 @@
         <v>82</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>-21</v>
       </c>
       <c r="M114" s="1"/>
@@ -12743,19 +13732,19 @@
         <v>66.72</v>
       </c>
       <c r="Q114" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>12.2</v>
       </c>
       <c r="R114" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>84.679999999999978</v>
       </c>
       <c r="S114" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>11.999999999999998</v>
       </c>
       <c r="T114" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5.0590163934426231</v>
       </c>
       <c r="U114" s="1">
@@ -12781,12 +13770,21 @@
       </c>
       <c r="AB114" s="1"/>
       <c r="AC114" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="AD114" s="1"/>
-      <c r="AE114" s="1"/>
-      <c r="AF114" s="1"/>
+      <c r="AD114" s="1">
+        <f t="shared" si="20"/>
+        <v>1.464</v>
+      </c>
+      <c r="AE114" s="1">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AF114" s="1">
+        <f t="shared" si="22"/>
+        <v>8.0063999999999993</v>
+      </c>
       <c r="AG114" s="1"/>
       <c r="AH114" s="1"/>
       <c r="AI114" s="1"/>
